--- a/Excel/Validasi/Hasil_Pengujian_Map_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_128_avg_length.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36951F5-51DA-4CBE-9A06-7837A10D6A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,18 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -237,8 +254,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,13 +318,1566 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Waktu Pencarian</a:t>
+            </a:r>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7.4070000000000006E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.502400000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.00845E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.197515</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-700E-4E04-83CA-0BB342A37D88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BDS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.103E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5548999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.2450000000000014E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.6299799999999991E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-700E-4E04-83CA-0BB342A37D88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8.0000000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1621000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.6097100000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1765678</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-700E-4E04-83CA-0BB342A37D88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7.4540000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1267999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.63918E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17614659999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-700E-4E04-83CA-0BB342A37D88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.5590000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9007E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.489E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.86468E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-700E-4E04-83CA-0BB342A37D88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PPO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7.8010000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.3932000000000008E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9090000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19919429999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-700E-4E04-83CA-0BB342A37D88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TPF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8.0730000000000005E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4716000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9246100000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19535810000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-700E-4E04-83CA-0BB342A37D88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1087391247"/>
+        <c:axId val="1087391727"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1087391247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087391727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1087391727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087391247"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7B3AE57-C6F6-C0C2-BD57-A9ED465E4AA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -345,7 +1915,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -379,6 +1949,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -413,9 +1984,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -588,11 +2160,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +2190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -623,22 +2198,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.0007407000000000001</v>
+        <v>7.4070000000000006E-4</v>
       </c>
       <c r="D2">
-        <v>0.004502400000000001</v>
+        <v>4.502400000000001E-3</v>
       </c>
       <c r="E2">
-        <v>0.0300845</v>
+        <v>3.00845E-2</v>
       </c>
       <c r="F2">
         <v>0.197515</v>
       </c>
       <c r="G2">
-        <v>0.05821065</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>5.8210650000000003E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -646,22 +2221,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.0004103</v>
+        <v>4.103E-4</v>
       </c>
       <c r="D3">
-        <v>0.0015549</v>
+        <v>1.5548999999999999E-3</v>
       </c>
       <c r="E3">
-        <v>0.006245000000000001</v>
+        <v>6.2450000000000014E-3</v>
       </c>
       <c r="F3">
-        <v>0.02629979999999999</v>
+        <v>2.6299799999999991E-2</v>
       </c>
       <c r="G3">
-        <v>0.0086275</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>8.6274999999999998E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -669,22 +2244,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="D4">
-        <v>0.0041621</v>
+        <v>4.1621000000000002E-3</v>
       </c>
       <c r="E4">
-        <v>0.0260971</v>
+        <v>2.6097100000000002E-2</v>
       </c>
       <c r="F4">
         <v>0.1765678</v>
       </c>
       <c r="G4">
-        <v>0.05190675</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>5.1906750000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -692,22 +2267,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.0007454</v>
+        <v>7.4540000000000001E-4</v>
       </c>
       <c r="D5">
-        <v>0.0041268</v>
+        <v>4.1267999999999999E-3</v>
       </c>
       <c r="E5">
-        <v>0.0263918</v>
+        <v>2.63918E-2</v>
       </c>
       <c r="F5">
-        <v>0.1761466</v>
+        <v>0.17614659999999999</v>
       </c>
       <c r="G5">
-        <v>0.05185265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>5.185265E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -715,22 +2290,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>0.0005559</v>
+        <v>5.5590000000000001E-4</v>
       </c>
       <c r="D6">
-        <v>0.0019007</v>
+        <v>1.9007E-3</v>
       </c>
       <c r="E6">
-        <v>0.007489</v>
+        <v>7.489E-3</v>
       </c>
       <c r="F6">
-        <v>0.0286468</v>
+        <v>2.86468E-2</v>
       </c>
       <c r="G6">
-        <v>0.0096481</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>9.6480999999999997E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -738,22 +2313,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>0.0007801</v>
+        <v>7.8010000000000004E-4</v>
       </c>
       <c r="D7">
-        <v>0.004393200000000001</v>
+        <v>4.3932000000000008E-3</v>
       </c>
       <c r="E7">
-        <v>0.02909</v>
+        <v>2.9090000000000001E-2</v>
       </c>
       <c r="F7">
-        <v>0.1991943</v>
+        <v>0.19919429999999999</v>
       </c>
       <c r="G7">
-        <v>0.0583644</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>5.8364399999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -761,22 +2336,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>0.0008073000000000001</v>
+        <v>8.0730000000000005E-4</v>
       </c>
       <c r="D8">
-        <v>0.0044716</v>
+        <v>4.4716000000000001E-3</v>
       </c>
       <c r="E8">
-        <v>0.0292461</v>
+        <v>2.9246100000000001E-2</v>
       </c>
       <c r="F8">
-        <v>0.1953581</v>
+        <v>0.19535810000000001</v>
       </c>
       <c r="G8">
-        <v>0.05747077499999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>5.7470774999999988E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -784,22 +2359,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>0.0004872</v>
+        <v>4.8720000000000002E-4</v>
       </c>
       <c r="D9">
-        <v>0.002411</v>
+        <v>2.4109999999999999E-3</v>
       </c>
       <c r="E9">
-        <v>0.0102976</v>
+        <v>1.0297600000000001E-2</v>
       </c>
       <c r="F9">
-        <v>0.05346799999999999</v>
+        <v>5.3467999999999988E-2</v>
       </c>
       <c r="G9">
-        <v>0.01666595</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>1.6665949999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -807,22 +2382,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>0.0003429</v>
+        <v>3.4289999999999999E-4</v>
       </c>
       <c r="D10">
-        <v>0.0015907</v>
+        <v>1.5907E-3</v>
       </c>
       <c r="E10">
-        <v>0.0069059</v>
+        <v>6.9059000000000004E-3</v>
       </c>
       <c r="F10">
-        <v>0.0308908</v>
+        <v>3.08908E-2</v>
       </c>
       <c r="G10">
-        <v>0.009932575000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>9.9325750000000008E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -830,22 +2405,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>0.000427</v>
+        <v>4.2700000000000002E-4</v>
       </c>
       <c r="D11">
-        <v>0.0016557</v>
+        <v>1.6557E-3</v>
       </c>
       <c r="E11">
-        <v>0.0065929</v>
+        <v>6.5928999999999996E-3</v>
       </c>
       <c r="F11">
-        <v>0.0274461</v>
+        <v>2.7446100000000001E-2</v>
       </c>
       <c r="G11">
-        <v>0.009030425</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>9.0304249999999999E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -853,22 +2428,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>0.0004355</v>
+        <v>4.3550000000000001E-4</v>
       </c>
       <c r="D12">
-        <v>0.0017736</v>
+        <v>1.7736E-3</v>
       </c>
       <c r="E12">
-        <v>0.006696199999999999</v>
+        <v>6.6961999999999994E-3</v>
       </c>
       <c r="F12">
-        <v>0.0278505</v>
+        <v>2.78505E-2</v>
       </c>
       <c r="G12">
-        <v>0.00918895</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>9.1889499999999995E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -876,22 +2451,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.0008449</v>
+        <v>8.4489999999999999E-4</v>
       </c>
       <c r="D13">
-        <v>0.0043894</v>
+        <v>4.3893999999999999E-3</v>
       </c>
       <c r="E13">
-        <v>0.0262355</v>
+        <v>2.6235499999999998E-2</v>
       </c>
       <c r="F13">
-        <v>0.1778364</v>
+        <v>0.17783640000000001</v>
       </c>
       <c r="G13">
-        <v>0.05232655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>5.2326549999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -899,22 +2474,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>0.0009634999999999999</v>
+        <v>9.6349999999999995E-4</v>
       </c>
       <c r="D14">
-        <v>0.004524100000000001</v>
+        <v>4.5241000000000014E-3</v>
       </c>
       <c r="E14">
-        <v>0.030114</v>
+        <v>3.0113999999999998E-2</v>
       </c>
       <c r="F14">
-        <v>0.1945541</v>
+        <v>0.19455410000000001</v>
       </c>
       <c r="G14">
-        <v>0.057538925</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>5.7538924999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -922,22 +2497,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>0.0009227</v>
+        <v>9.2270000000000004E-4</v>
       </c>
       <c r="D15">
-        <v>0.0054286</v>
+        <v>5.4285999999999996E-3</v>
       </c>
       <c r="E15">
-        <v>0.03332020000000001</v>
+        <v>3.3320200000000008E-2</v>
       </c>
       <c r="F15">
-        <v>0.2227611</v>
+        <v>0.22276109999999999</v>
       </c>
       <c r="G15">
-        <v>0.06560815</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>6.5608150000000004E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -945,22 +2520,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>0.0007974</v>
+        <v>7.9739999999999998E-4</v>
       </c>
       <c r="D16">
-        <v>0.0042241</v>
+        <v>4.2240999999999997E-3</v>
       </c>
       <c r="E16">
-        <v>0.0265063</v>
+        <v>2.65063E-2</v>
       </c>
       <c r="F16">
         <v>0.1774308</v>
       </c>
       <c r="G16">
-        <v>0.05223965000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>5.2239650000000012E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -968,22 +2543,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>0.0007744</v>
+        <v>7.7439999999999996E-4</v>
       </c>
       <c r="D17">
-        <v>0.0043771</v>
+        <v>4.3771000000000001E-3</v>
       </c>
       <c r="E17">
-        <v>0.0256845</v>
+        <v>2.5684499999999999E-2</v>
       </c>
       <c r="F17">
-        <v>0.1653185</v>
+        <v>0.16531850000000001</v>
       </c>
       <c r="G17">
-        <v>0.049038625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>4.9038625000000002E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -991,22 +2566,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>0.0004264000000000001</v>
+        <v>4.2640000000000012E-4</v>
       </c>
       <c r="D18">
-        <v>0.0014403</v>
+        <v>1.4403E-3</v>
       </c>
       <c r="E18">
-        <v>0.0046153</v>
+        <v>4.6153000000000001E-3</v>
       </c>
       <c r="F18">
-        <v>0.0164178</v>
+        <v>1.64178E-2</v>
       </c>
       <c r="G18">
-        <v>0.005724950000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>5.7249500000000012E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1014,22 +2589,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>0.0004348999999999999</v>
+        <v>4.3489999999999989E-4</v>
       </c>
       <c r="D19">
-        <v>0.0014727</v>
+        <v>1.4727E-3</v>
       </c>
       <c r="E19">
-        <v>0.004426100000000001</v>
+        <v>4.4261000000000014E-3</v>
       </c>
       <c r="F19">
-        <v>0.0149537</v>
+        <v>1.49537E-2</v>
       </c>
       <c r="G19">
-        <v>0.005321849999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>5.3218499999999986E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1037,22 +2612,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>0.0005702999999999999</v>
+        <v>5.7029999999999993E-4</v>
       </c>
       <c r="D20">
-        <v>0.0017755</v>
+        <v>1.7755E-3</v>
       </c>
       <c r="E20">
-        <v>0.0062226</v>
+        <v>6.2226E-3</v>
       </c>
       <c r="F20">
-        <v>0.0227431</v>
+        <v>2.2743099999999999E-2</v>
       </c>
       <c r="G20">
-        <v>0.007827875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>7.8278749999999998E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -1060,22 +2635,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>0.0005624</v>
+        <v>5.6240000000000001E-4</v>
       </c>
       <c r="D21">
-        <v>0.0019664</v>
+        <v>1.9664000000000001E-3</v>
       </c>
       <c r="E21">
-        <v>0.007500999999999999</v>
+        <v>7.500999999999999E-3</v>
       </c>
       <c r="F21">
-        <v>0.0286817</v>
+        <v>2.8681700000000001E-2</v>
       </c>
       <c r="G21">
-        <v>0.009677874999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>9.677874999999999E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1083,22 +2658,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>0.0005455</v>
+        <v>5.4549999999999998E-4</v>
       </c>
       <c r="D22">
-        <v>0.0021722</v>
+        <v>2.1722E-3</v>
       </c>
       <c r="E22">
-        <v>0.008067300000000001</v>
+        <v>8.0673000000000012E-3</v>
       </c>
       <c r="F22">
-        <v>0.031123</v>
+        <v>3.1123000000000001E-2</v>
       </c>
       <c r="G22">
-        <v>0.010477</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>1.0477E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -1106,22 +2681,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>0.0008457999999999999</v>
+        <v>8.4579999999999985E-4</v>
       </c>
       <c r="D23">
-        <v>0.0045512</v>
+        <v>4.5512E-3</v>
       </c>
       <c r="E23">
-        <v>0.0293555</v>
+        <v>2.93555E-2</v>
       </c>
       <c r="F23">
-        <v>0.195447</v>
+        <v>0.19544700000000001</v>
       </c>
       <c r="G23">
-        <v>0.05754987499999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>5.7549874999999993E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1129,22 +2704,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>0.0005317000000000001</v>
+        <v>5.3170000000000008E-4</v>
       </c>
       <c r="D24">
-        <v>0.0025243</v>
+        <v>2.5243000000000002E-3</v>
       </c>
       <c r="E24">
-        <v>0.0107272</v>
+        <v>1.0727199999999999E-2</v>
       </c>
       <c r="F24">
-        <v>0.0546624</v>
+        <v>5.46624E-2</v>
       </c>
       <c r="G24">
-        <v>0.0171114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>1.7111399999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1152,22 +2727,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>0.0005423</v>
+        <v>5.4230000000000001E-4</v>
       </c>
       <c r="D25">
-        <v>0.002314</v>
+        <v>2.3140000000000001E-3</v>
       </c>
       <c r="E25">
-        <v>0.0113215</v>
+        <v>1.13215E-2</v>
       </c>
       <c r="F25">
-        <v>0.053804</v>
+        <v>5.3803999999999998E-2</v>
       </c>
       <c r="G25">
-        <v>0.01699545</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>1.6995449999999999E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -1175,22 +2750,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>0.0005289</v>
+        <v>5.2890000000000001E-4</v>
       </c>
       <c r="D26">
-        <v>0.0025884</v>
+        <v>2.5883999999999998E-3</v>
       </c>
       <c r="E26">
-        <v>0.011309</v>
+        <v>1.1309E-2</v>
       </c>
       <c r="F26">
-        <v>0.0581127</v>
+        <v>5.8112700000000003E-2</v>
       </c>
       <c r="G26">
-        <v>0.01813475</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>1.8134750000000002E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1198,22 +2773,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0003904</v>
+        <v>3.904E-4</v>
       </c>
       <c r="D27">
-        <v>0.0017126</v>
+        <v>1.7126000000000001E-3</v>
       </c>
       <c r="E27">
-        <v>0.0072632</v>
+        <v>7.2632E-3</v>
       </c>
       <c r="F27">
-        <v>0.0316003</v>
+        <v>3.1600299999999998E-2</v>
       </c>
       <c r="G27">
-        <v>0.010241625</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>1.0241625000000001E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -1221,22 +2796,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>0.0003991</v>
+        <v>3.991E-4</v>
       </c>
       <c r="D28">
-        <v>0.0017038</v>
+        <v>1.7038000000000001E-3</v>
       </c>
       <c r="E28">
-        <v>0.006988299999999999</v>
+        <v>6.9882999999999994E-3</v>
       </c>
       <c r="F28">
-        <v>0.0313834</v>
+        <v>3.1383399999999999E-2</v>
       </c>
       <c r="G28">
-        <v>0.01011865</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>1.011865E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -1244,22 +2819,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>0.0004798</v>
+        <v>4.7980000000000001E-4</v>
       </c>
       <c r="D29">
-        <v>0.0018871</v>
+        <v>1.8871000000000001E-3</v>
       </c>
       <c r="E29">
-        <v>0.006968200000000001</v>
+        <v>6.9682000000000008E-3</v>
       </c>
       <c r="F29">
-        <v>0.0289323</v>
+        <v>2.8932300000000001E-2</v>
       </c>
       <c r="G29">
-        <v>0.00956685</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>9.56685E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1267,22 +2842,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>0.0009962000000000003</v>
+        <v>9.9620000000000025E-4</v>
       </c>
       <c r="D30">
-        <v>0.004606399999999999</v>
+        <v>4.6063999999999992E-3</v>
       </c>
       <c r="E30">
-        <v>0.0300677</v>
+        <v>3.0067699999999999E-2</v>
       </c>
       <c r="F30">
-        <v>0.1960388</v>
+        <v>0.19603880000000001</v>
       </c>
       <c r="G30">
-        <v>0.057927275</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>5.7927275E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1290,22 +2865,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>0.0009992999999999998</v>
+        <v>9.9929999999999984E-4</v>
       </c>
       <c r="D31">
-        <v>0.0054957</v>
+        <v>5.4957000000000001E-3</v>
       </c>
       <c r="E31">
-        <v>0.0334449</v>
+        <v>3.34449E-2</v>
       </c>
       <c r="F31">
         <v>0.2236168</v>
       </c>
       <c r="G31">
-        <v>0.06588917499999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>6.5889174999999994E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1313,22 +2888,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>0.0009961999999999998</v>
+        <v>9.9619999999999982E-4</v>
       </c>
       <c r="D32">
-        <v>0.0056181</v>
+        <v>5.6181E-3</v>
       </c>
       <c r="E32">
-        <v>0.0328473</v>
+        <v>3.2847300000000003E-2</v>
       </c>
       <c r="F32">
-        <v>0.2163768</v>
+        <v>0.21637680000000001</v>
       </c>
       <c r="G32">
-        <v>0.06395960000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>6.3959600000000005E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -1336,22 +2911,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>0.0008156</v>
+        <v>8.1559999999999998E-4</v>
       </c>
       <c r="D33">
-        <v>0.004460800000000001</v>
+        <v>4.4608000000000009E-3</v>
       </c>
       <c r="E33">
-        <v>0.0262301</v>
+        <v>2.6230099999999999E-2</v>
       </c>
       <c r="F33">
-        <v>0.1662655</v>
+        <v>0.16626550000000001</v>
       </c>
       <c r="G33">
-        <v>0.049443</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>4.9443000000000001E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -1359,22 +2934,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>0.0004229</v>
+        <v>4.2289999999999998E-4</v>
       </c>
       <c r="D34">
-        <v>0.0012852</v>
+        <v>1.2852E-3</v>
       </c>
       <c r="E34">
-        <v>0.003945700000000001</v>
+        <v>3.9457000000000008E-3</v>
       </c>
       <c r="F34">
-        <v>0.0136457</v>
+        <v>1.36457E-2</v>
       </c>
       <c r="G34">
-        <v>0.004824875</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>4.8248750000000002E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1382,22 +2957,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>0.0002601</v>
+        <v>2.6009999999999998E-4</v>
       </c>
       <c r="D35">
-        <v>0.0008677000000000001</v>
+        <v>8.6770000000000011E-4</v>
       </c>
       <c r="E35">
-        <v>0.0028971</v>
+        <v>2.8971000000000001E-3</v>
       </c>
       <c r="F35">
-        <v>0.0106531</v>
+        <v>1.06531E-2</v>
       </c>
       <c r="G35">
-        <v>0.0036695</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>3.6695E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -1405,22 +2980,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>0.0004631</v>
+        <v>4.6309999999999998E-4</v>
       </c>
       <c r="D36">
-        <v>0.0015038</v>
+        <v>1.5038E-3</v>
       </c>
       <c r="E36">
-        <v>0.004717999999999999</v>
+        <v>4.7179999999999991E-3</v>
       </c>
       <c r="F36">
-        <v>0.0166801</v>
+        <v>1.66801E-2</v>
       </c>
       <c r="G36">
-        <v>0.005841249999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>5.8412499999999992E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -1428,22 +3003,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>0.0003868</v>
+        <v>3.8680000000000002E-4</v>
       </c>
       <c r="D37">
-        <v>0.0011697</v>
+        <v>1.1697000000000001E-3</v>
       </c>
       <c r="E37">
-        <v>0.0040164</v>
+        <v>4.0163999999999998E-3</v>
       </c>
       <c r="F37">
-        <v>0.018203</v>
+        <v>1.8203E-2</v>
       </c>
       <c r="G37">
-        <v>0.005943975</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>5.9439749999999998E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -1451,22 +3026,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>0.0004904999999999999</v>
+        <v>4.9049999999999994E-4</v>
       </c>
       <c r="D38">
-        <v>0.0015409</v>
+        <v>1.5409E-3</v>
       </c>
       <c r="E38">
-        <v>0.004481</v>
+        <v>4.4809999999999997E-3</v>
       </c>
       <c r="F38">
-        <v>0.0150447</v>
+        <v>1.5044699999999999E-2</v>
       </c>
       <c r="G38">
-        <v>0.005389275</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>5.3892749999999998E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -1474,22 +3049,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>0.0004544</v>
+        <v>4.5439999999999999E-4</v>
       </c>
       <c r="D39">
-        <v>0.0014839</v>
+        <v>1.4839E-3</v>
       </c>
       <c r="E39">
-        <v>0.0037844</v>
+        <v>3.7843999999999998E-3</v>
       </c>
       <c r="F39">
-        <v>0.0127733</v>
+        <v>1.27733E-2</v>
       </c>
       <c r="G39">
-        <v>0.004624</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>4.6239999999999996E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1497,22 +3072,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>0.0005122</v>
+        <v>5.1219999999999998E-4</v>
       </c>
       <c r="D40">
-        <v>0.0015761</v>
+        <v>1.5761E-3</v>
       </c>
       <c r="E40">
-        <v>0.004443</v>
+        <v>4.4429999999999999E-3</v>
       </c>
       <c r="F40">
-        <v>0.0164645</v>
+        <v>1.64645E-2</v>
       </c>
       <c r="G40">
-        <v>0.00574895</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>5.7489500000000001E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -1520,22 +3095,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>0.0006249999999999999</v>
+        <v>6.249999999999999E-4</v>
       </c>
       <c r="D41">
-        <v>0.0018004</v>
+        <v>1.8004E-3</v>
       </c>
       <c r="E41">
-        <v>0.006223100000000001</v>
+        <v>6.2231000000000014E-3</v>
       </c>
       <c r="F41">
-        <v>0.022878</v>
+        <v>2.2877999999999999E-2</v>
       </c>
       <c r="G41">
-        <v>0.007881625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>7.8816249999999997E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -1543,22 +3118,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>0.0006505</v>
+        <v>6.5050000000000004E-4</v>
       </c>
       <c r="D42">
-        <v>0.0018184</v>
+        <v>1.8184E-3</v>
       </c>
       <c r="E42">
-        <v>0.005675599999999999</v>
+        <v>5.6755999999999994E-3</v>
       </c>
       <c r="F42">
-        <v>0.0214289</v>
+        <v>2.1428900000000001E-2</v>
       </c>
       <c r="G42">
-        <v>0.00739335</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>7.3933499999999999E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -1566,22 +3141,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>0.0005898</v>
+        <v>5.8980000000000002E-4</v>
       </c>
       <c r="D43">
-        <v>0.0022073</v>
+        <v>2.2073000000000001E-3</v>
       </c>
       <c r="E43">
-        <v>0.008251400000000001</v>
+        <v>8.2514000000000007E-3</v>
       </c>
       <c r="F43">
-        <v>0.031252</v>
+        <v>3.1252000000000002E-2</v>
       </c>
       <c r="G43">
-        <v>0.010575125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>1.0575124999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -1589,22 +3164,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>0.0006048000000000001</v>
+        <v>6.0480000000000006E-4</v>
       </c>
       <c r="D44">
-        <v>0.0024552</v>
+        <v>2.4551999999999998E-3</v>
       </c>
       <c r="E44">
-        <v>0.011688</v>
+        <v>1.1688E-2</v>
       </c>
       <c r="F44">
-        <v>0.0550986</v>
+        <v>5.5098599999999998E-2</v>
       </c>
       <c r="G44">
-        <v>0.01746165</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>1.7461649999999999E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1612,22 +3187,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>0.0005555</v>
+        <v>5.555E-4</v>
       </c>
       <c r="D45">
-        <v>0.0027221</v>
+        <v>2.7220999999999999E-3</v>
       </c>
       <c r="E45">
-        <v>0.0117139</v>
+        <v>1.1713899999999999E-2</v>
       </c>
       <c r="F45">
-        <v>0.0588957</v>
+        <v>5.8895700000000002E-2</v>
       </c>
       <c r="G45">
-        <v>0.0184718</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>1.84718E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -1635,22 +3210,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>0.0005543</v>
+        <v>5.5429999999999998E-4</v>
       </c>
       <c r="D46">
-        <v>0.0027088</v>
+        <v>2.7087999999999999E-3</v>
       </c>
       <c r="E46">
-        <v>0.0109618</v>
+        <v>1.0961800000000001E-2</v>
       </c>
       <c r="F46">
-        <v>0.0556443</v>
+        <v>5.5644300000000001E-2</v>
       </c>
       <c r="G46">
-        <v>0.0174673</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>1.7467300000000002E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -1658,22 +3233,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>0.0004518</v>
+        <v>4.5179999999999998E-4</v>
       </c>
       <c r="D47">
-        <v>0.0018246</v>
+        <v>1.8246E-3</v>
       </c>
       <c r="E47">
-        <v>0.007335</v>
+        <v>7.3350000000000004E-3</v>
       </c>
       <c r="F47">
-        <v>0.0325033</v>
+        <v>3.2503299999999999E-2</v>
       </c>
       <c r="G47">
-        <v>0.010528675</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>1.0528674999999999E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -1681,22 +3256,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>0.0010834</v>
+        <v>1.0834E-3</v>
       </c>
       <c r="D48">
-        <v>0.0057332</v>
+        <v>5.7331999999999999E-3</v>
       </c>
       <c r="E48">
-        <v>0.0330536</v>
+        <v>3.3053600000000002E-2</v>
       </c>
       <c r="F48">
-        <v>0.2178838</v>
+        <v>0.21788379999999999</v>
       </c>
       <c r="G48">
-        <v>0.06443850000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>6.443850000000001E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -1704,22 +3279,22 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>0.0004573</v>
+        <v>4.573E-4</v>
       </c>
       <c r="D49">
-        <v>0.0013416</v>
+        <v>1.3416000000000001E-3</v>
       </c>
       <c r="E49">
-        <v>0.0040723</v>
+        <v>4.0723000000000001E-3</v>
       </c>
       <c r="F49">
-        <v>0.0138525</v>
+        <v>1.38525E-2</v>
       </c>
       <c r="G49">
-        <v>0.004930924999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>4.9309249999999992E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1727,22 +3302,22 @@
         <v>55</v>
       </c>
       <c r="C50">
-        <v>0.0004141</v>
+        <v>4.1409999999999998E-4</v>
       </c>
       <c r="D50">
-        <v>0.0014135</v>
+        <v>1.4135E-3</v>
       </c>
       <c r="E50">
-        <v>0.0039064</v>
+        <v>3.9064E-3</v>
       </c>
       <c r="F50">
-        <v>0.0150885</v>
+        <v>1.5088499999999999E-2</v>
       </c>
       <c r="G50">
-        <v>0.005205625</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>5.2056250000000002E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -1750,22 +3325,22 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>0.0003168</v>
+        <v>3.168E-4</v>
       </c>
       <c r="D51">
-        <v>0.0009419999999999999</v>
+        <v>9.4199999999999991E-4</v>
       </c>
       <c r="E51">
-        <v>0.0029469</v>
+        <v>2.9469000000000001E-3</v>
       </c>
       <c r="F51">
-        <v>0.0107509</v>
+        <v>1.0750900000000001E-2</v>
       </c>
       <c r="G51">
-        <v>0.00373915</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>3.7391500000000001E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -1773,22 +3348,22 @@
         <v>57</v>
       </c>
       <c r="C52">
-        <v>0.0003</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="D52">
-        <v>0.0009570000000000001</v>
+        <v>9.5700000000000006E-4</v>
       </c>
       <c r="E52">
-        <v>0.0030205</v>
+        <v>3.0205000000000002E-3</v>
       </c>
       <c r="F52">
-        <v>0.0108284</v>
+        <v>1.08284E-2</v>
       </c>
       <c r="G52">
-        <v>0.003776475</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>3.7764750000000001E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -1796,22 +3371,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>0.0002973</v>
+        <v>2.9730000000000002E-4</v>
       </c>
       <c r="D53">
-        <v>0.0009595000000000001</v>
+        <v>9.5950000000000007E-4</v>
       </c>
       <c r="E53">
-        <v>0.003853</v>
+        <v>3.8530000000000001E-3</v>
       </c>
       <c r="F53">
-        <v>0.0185579</v>
+        <v>1.8557899999999999E-2</v>
       </c>
       <c r="G53">
-        <v>0.005916925</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>5.916925E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -1819,22 +3394,22 @@
         <v>59</v>
       </c>
       <c r="C54">
-        <v>0.0004243</v>
+        <v>4.2430000000000001E-4</v>
       </c>
       <c r="D54">
-        <v>0.0012128</v>
+        <v>1.2128E-3</v>
       </c>
       <c r="E54">
-        <v>0.0041151</v>
+        <v>4.1151E-3</v>
       </c>
       <c r="F54">
-        <v>0.0183518</v>
+        <v>1.8351800000000001E-2</v>
       </c>
       <c r="G54">
-        <v>0.006025999999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>6.0259999999999992E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -1842,22 +3417,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>0.0005036</v>
+        <v>5.0359999999999999E-4</v>
       </c>
       <c r="D55">
-        <v>0.0016622</v>
+        <v>1.6622E-3</v>
       </c>
       <c r="E55">
-        <v>0.0039161</v>
+        <v>3.9160999999999996E-3</v>
       </c>
       <c r="F55">
-        <v>0.0129379</v>
+        <v>1.29379E-2</v>
       </c>
       <c r="G55">
-        <v>0.004754949999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>4.7549499999999991E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -1865,22 +3440,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>0.0005664</v>
+        <v>5.664E-4</v>
       </c>
       <c r="D56">
-        <v>0.0016503</v>
+        <v>1.6502999999999999E-3</v>
       </c>
       <c r="E56">
-        <v>0.004534300000000001</v>
+        <v>4.5343000000000007E-3</v>
       </c>
       <c r="F56">
-        <v>0.0166175</v>
+        <v>1.66175E-2</v>
       </c>
       <c r="G56">
-        <v>0.005842125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>5.8421250000000001E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -1888,22 +3463,22 @@
         <v>62</v>
       </c>
       <c r="C57">
-        <v>0.0005223999999999999</v>
+        <v>5.223999999999999E-4</v>
       </c>
       <c r="D57">
-        <v>0.0017146</v>
+        <v>1.7145999999999999E-3</v>
       </c>
       <c r="E57">
-        <v>0.0044987</v>
+        <v>4.4986999999999996E-3</v>
       </c>
       <c r="F57">
-        <v>0.0164548</v>
+        <v>1.6454799999999999E-2</v>
       </c>
       <c r="G57">
-        <v>0.005797625000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>5.7976250000000007E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -1911,22 +3486,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>0.0006255999999999999</v>
+        <v>6.2559999999999992E-4</v>
       </c>
       <c r="D58">
-        <v>0.0018471</v>
+        <v>1.8471E-3</v>
       </c>
       <c r="E58">
-        <v>0.005797099999999999</v>
+        <v>5.7970999999999986E-3</v>
       </c>
       <c r="F58">
-        <v>0.0215302</v>
+        <v>2.1530199999999999E-2</v>
       </c>
       <c r="G58">
-        <v>0.00745</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>7.45E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -1934,22 +3509,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>0.0006153</v>
+        <v>6.1530000000000005E-4</v>
       </c>
       <c r="D59">
-        <v>0.0027614</v>
+        <v>2.7613999999999998E-3</v>
       </c>
       <c r="E59">
-        <v>0.0113934</v>
+        <v>1.13934E-2</v>
       </c>
       <c r="F59">
-        <v>0.05662929999999999</v>
+        <v>5.6629299999999987E-2</v>
       </c>
       <c r="G59">
-        <v>0.01784985</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>1.784985E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -1957,22 +3532,22 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>0.0004642</v>
+        <v>4.6420000000000001E-4</v>
       </c>
       <c r="D60">
-        <v>0.0013606</v>
+        <v>1.3606E-3</v>
       </c>
       <c r="E60">
-        <v>0.003989499999999999</v>
+        <v>3.9894999999999991E-3</v>
       </c>
       <c r="F60">
-        <v>0.015263</v>
+        <v>1.5263000000000001E-2</v>
       </c>
       <c r="G60">
-        <v>0.005269324999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>5.2693249999999992E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -1980,22 +3555,22 @@
         <v>66</v>
       </c>
       <c r="C61">
-        <v>0.0003617</v>
+        <v>3.6170000000000001E-4</v>
       </c>
       <c r="D61">
-        <v>0.0010395</v>
+        <v>1.0395000000000001E-3</v>
       </c>
       <c r="E61">
-        <v>0.0030456</v>
+        <v>3.0455999999999999E-3</v>
       </c>
       <c r="F61">
-        <v>0.0109078</v>
+        <v>1.09078E-2</v>
       </c>
       <c r="G61">
-        <v>0.00383865</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>3.8386499999999999E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -2003,22 +3578,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>0.0003448</v>
+        <v>3.4479999999999998E-4</v>
       </c>
       <c r="D62">
-        <v>0.0009938</v>
+        <v>9.9379999999999998E-4</v>
       </c>
       <c r="E62">
-        <v>0.0034226</v>
+        <v>3.4226E-3</v>
       </c>
       <c r="F62">
-        <v>0.0172666</v>
+        <v>1.72666E-2</v>
       </c>
       <c r="G62">
-        <v>0.00550695</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>5.50695E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -2026,22 +3601,22 @@
         <v>68</v>
       </c>
       <c r="C63">
-        <v>0.0003387999999999999</v>
+        <v>3.3879999999999989E-4</v>
       </c>
       <c r="D63">
-        <v>0.0010177</v>
+        <v>1.0177000000000001E-3</v>
       </c>
       <c r="E63">
-        <v>0.0039006</v>
+        <v>3.9006000000000002E-3</v>
       </c>
       <c r="F63">
-        <v>0.0187464</v>
+        <v>1.87464E-2</v>
       </c>
       <c r="G63">
-        <v>0.006000875</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>6.0008750000000001E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -2049,22 +3624,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>0.0005491</v>
+        <v>5.4909999999999996E-4</v>
       </c>
       <c r="D64">
-        <v>0.0016805</v>
+        <v>1.6804999999999999E-3</v>
       </c>
       <c r="E64">
-        <v>0.004568300000000001</v>
+        <v>4.5683000000000008E-3</v>
       </c>
       <c r="F64">
-        <v>0.0165769</v>
+        <v>1.6576899999999999E-2</v>
       </c>
       <c r="G64">
-        <v>0.0058437</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>5.8437000000000003E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -2072,32 +3647,33 @@
         <v>70</v>
       </c>
       <c r="C65">
-        <v>0.0003677</v>
+        <v>3.6769999999999999E-4</v>
       </c>
       <c r="D65">
-        <v>0.0012076</v>
+        <v>1.2076000000000001E-3</v>
       </c>
       <c r="E65">
-        <v>0.0035401</v>
+        <v>3.5401E-3</v>
       </c>
       <c r="F65">
-        <v>0.0173821</v>
+        <v>1.7382100000000001E-2</v>
       </c>
       <c r="G65">
-        <v>0.005624375</v>
+        <v>5.624375E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2120,7 +3696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2143,7 +3719,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2166,7 +3742,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2189,7 +3765,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2212,7 +3788,7 @@
         <v>89.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2235,7 +3811,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2258,7 +3834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2281,7 +3857,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2304,7 +3880,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2327,7 +3903,7 @@
         <v>90.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2350,7 +3926,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2373,7 +3949,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2396,7 +3972,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2419,7 +3995,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2442,7 +4018,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2465,7 +4041,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2488,7 +4064,7 @@
         <v>89.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2511,7 +4087,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2534,7 +4110,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2557,7 +4133,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2580,7 +4156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2603,7 +4179,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -2626,7 +4202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2649,7 +4225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2672,7 +4248,7 @@
         <v>90.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2695,7 +4271,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2718,7 +4294,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2741,7 +4317,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2764,7 +4340,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2787,7 +4363,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2810,7 +4386,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2833,7 +4409,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2856,7 +4432,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2879,7 +4455,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2902,7 +4478,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2925,7 +4501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2948,7 +4524,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2971,7 +4547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -2994,7 +4570,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3017,7 +4593,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -3040,7 +4616,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -3063,7 +4639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -3086,7 +4662,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3109,7 +4685,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3132,7 +4708,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3155,7 +4731,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3178,7 +4754,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -3201,7 +4777,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -3224,7 +4800,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3247,7 +4823,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -3270,7 +4846,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -3293,7 +4869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3316,7 +4892,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -3339,7 +4915,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -3362,7 +4938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -3385,7 +4961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -3408,7 +4984,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -3431,7 +5007,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -3454,7 +5030,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -3477,7 +5053,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -3500,7 +5076,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -3523,7 +5099,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -3546,7 +5122,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -3569,7 +5145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -3598,11 +5174,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +5204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3633,22 +5212,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D2">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E2">
         <v>105.4974746830583</v>
       </c>
       <c r="F2">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G2">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3656,7 +5235,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>26.14213562373095</v>
+        <v>26.142135623730951</v>
       </c>
       <c r="D3">
         <v>52.87005768508881</v>
@@ -3665,13 +5244,13 @@
         <v>105.4974746830583</v>
       </c>
       <c r="F3">
-        <v>213.2375900532359</v>
+        <v>213.23759005323589</v>
       </c>
       <c r="G3">
-        <v>99.4368145112785</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>99.436814511278499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3682,7 +5261,7 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D4">
-        <v>57.69848480983499</v>
+        <v>57.698484809834987</v>
       </c>
       <c r="E4">
         <v>117.9827560572969</v>
@@ -3694,7 +5273,7 @@
         <v>110.4472221513642</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3702,10 +5281,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D5">
-        <v>53.21320343559643</v>
+        <v>53.213203435596427</v>
       </c>
       <c r="E5">
         <v>107.8406204335659</v>
@@ -3714,10 +5293,10 @@
         <v>217.095454429505</v>
       </c>
       <c r="G5">
-        <v>100.865746699413</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>100.86574669941299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3725,22 +5304,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D6">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E6">
         <v>105.4974746830583</v>
       </c>
       <c r="F6">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G6">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3751,19 +5330,19 @@
         <v>24.66630939248272</v>
       </c>
       <c r="D7">
-        <v>50.44927995330885</v>
+        <v>50.449279953308853</v>
       </c>
       <c r="E7">
         <v>101.6951293341927</v>
       </c>
       <c r="F7">
-        <v>203.5674336095196</v>
+        <v>203.56743360951961</v>
       </c>
       <c r="G7">
-        <v>95.09453807237597</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>95.094538072375968</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3771,22 +5350,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D8">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E8">
         <v>105.4974746830583</v>
       </c>
       <c r="F8">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G8">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3797,19 +5376,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D9">
-        <v>56.52691193458119</v>
+        <v>56.526911934581193</v>
       </c>
       <c r="E9">
-        <v>114.4680374315355</v>
+        <v>114.46803743153551</v>
       </c>
       <c r="F9">
-        <v>230.350288425444</v>
+        <v>230.35028842544401</v>
       </c>
       <c r="G9">
         <v>107.2253967444162</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3820,19 +5399,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D10">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E10">
         <v>111.9827560572969</v>
       </c>
       <c r="F10">
-        <v>225.1370849898476</v>
+        <v>225.13708498984761</v>
       </c>
       <c r="G10">
         <v>105.0936687607709</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3840,22 +5419,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>24.79972471294712</v>
+        <v>24.799724712947121</v>
       </c>
       <c r="D11">
-        <v>51.29784446040809</v>
+        <v>51.297844460408093</v>
       </c>
       <c r="E11">
-        <v>102.6667298324277</v>
+        <v>102.66672983242771</v>
       </c>
       <c r="F11">
-        <v>203.5337904137645</v>
+        <v>203.53379041376451</v>
       </c>
       <c r="G11">
-        <v>95.57452235488685</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>95.574522354886852</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3863,7 +5442,7 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D12">
         <v>52.87005768508881</v>
@@ -3872,13 +5451,13 @@
         <v>106.3259018078045</v>
       </c>
       <c r="F12">
-        <v>213.2375900532359</v>
+        <v>213.23759005323589</v>
       </c>
       <c r="G12">
-        <v>99.4368145112785</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>99.436814511278499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3895,13 +5474,13 @@
         <v>109.5990165731959</v>
       </c>
       <c r="F13">
-        <v>219.4687012837836</v>
+        <v>219.46870128378359</v>
       </c>
       <c r="G13">
-        <v>102.6426028580128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>102.64260285801279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3909,22 +5488,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>28.38477631085023</v>
+        <v>28.384776310850231</v>
       </c>
       <c r="D14">
-        <v>58.52691193458119</v>
+        <v>58.526911934581193</v>
       </c>
       <c r="E14">
-        <v>120.4680374315355</v>
+        <v>120.46803743153551</v>
       </c>
       <c r="F14">
-        <v>242.6934341759516</v>
+        <v>242.69343417595161</v>
       </c>
       <c r="G14">
-        <v>112.5182899632296</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>112.51828996322961</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3932,22 +5511,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>28.38477631085023</v>
+        <v>28.384776310850231</v>
       </c>
       <c r="D15">
-        <v>56.52691193458119</v>
+        <v>56.526911934581193</v>
       </c>
       <c r="E15">
         <v>118.8111831820431</v>
       </c>
       <c r="F15">
-        <v>237.7228714274746</v>
+        <v>237.72287142747459</v>
       </c>
       <c r="G15">
-        <v>110.3614357137373</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>110.36143571373729</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3955,22 +5534,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>25.02260056222932</v>
+        <v>25.022600562229321</v>
       </c>
       <c r="D16">
-        <v>51.95521971873434</v>
+        <v>51.955219718734341</v>
       </c>
       <c r="E16">
-        <v>104.2952231567888</v>
+        <v>104.29522315678879</v>
       </c>
       <c r="F16">
-        <v>208.2523221830841</v>
+        <v>208.25232218308409</v>
       </c>
       <c r="G16">
-        <v>97.38134140520916</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>97.381341405209156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3978,10 +5557,10 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D17">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E17">
         <v>107.8406204335659</v>
@@ -3993,7 +5572,7 @@
         <v>100.5728534805996</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4001,22 +5580,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D18">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E18">
         <v>105.4974746830583</v>
       </c>
       <c r="F18">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G18">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4027,19 +5606,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D19">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E19">
         <v>111.9827560572969</v>
       </c>
       <c r="F19">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G19">
         <v>104.9472221513642</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4047,10 +5626,10 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D20">
-        <v>53.21320343559643</v>
+        <v>53.213203435596427</v>
       </c>
       <c r="E20">
         <v>107.8406204335659</v>
@@ -4059,10 +5638,10 @@
         <v>217.095454429505</v>
       </c>
       <c r="G20">
-        <v>100.865746699413</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>100.86574669941299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4070,22 +5649,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>24.95741732923815</v>
+        <v>24.957417329238151</v>
       </c>
       <c r="D21">
-        <v>51.32904822084939</v>
+        <v>51.329048220849387</v>
       </c>
       <c r="E21">
-        <v>104.0723100040719</v>
+        <v>104.07231000407189</v>
       </c>
       <c r="F21">
         <v>209.5588335705169</v>
       </c>
       <c r="G21">
-        <v>97.47940228116909</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>97.479402281169087</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4093,22 +5672,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D22">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E22">
         <v>111.9827560572969</v>
       </c>
       <c r="F22">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G22">
         <v>104.3865619795843</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4116,22 +5695,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>25.02260056222932</v>
+        <v>25.022600562229321</v>
       </c>
       <c r="D23">
-        <v>50.06836276930867</v>
+        <v>50.068362769308671</v>
       </c>
       <c r="E23">
         <v>101.6951293341927</v>
       </c>
       <c r="F23">
-        <v>204.9948409258163</v>
+        <v>204.99484092581631</v>
       </c>
       <c r="G23">
-        <v>95.44523339788677</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>95.445233397886767</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4139,22 +5718,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>27.07974332476231</v>
+        <v>27.079743324762308</v>
       </c>
       <c r="D24">
-        <v>54.52033108787928</v>
+        <v>54.520331087879278</v>
       </c>
       <c r="E24">
-        <v>109.3695959086591</v>
+        <v>109.36959590865909</v>
       </c>
       <c r="F24">
-        <v>217.2742268734918</v>
+        <v>217.27422687349181</v>
       </c>
       <c r="G24">
         <v>102.0609742986981</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4165,19 +5744,19 @@
         <v>28.97056274847715</v>
       </c>
       <c r="D25">
-        <v>57.94112549695429</v>
+        <v>57.941125496954292</v>
       </c>
       <c r="E25">
         <v>117.5391052434009</v>
       </c>
       <c r="F25">
-        <v>234.492424049175</v>
+        <v>234.49242404917501</v>
       </c>
       <c r="G25">
         <v>109.7358043845018</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4188,19 +5767,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D26">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E26">
         <v>111.9827560572969</v>
       </c>
       <c r="F26">
-        <v>225.7228714274746</v>
+        <v>225.72287142747459</v>
       </c>
       <c r="G26">
-        <v>105.2401153701776</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>105.24011537017761</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4214,16 +5793,16 @@
         <v>54.69243699517763</v>
       </c>
       <c r="E27">
-        <v>109.4612036670544</v>
+        <v>109.46120366705441</v>
       </c>
       <c r="F27">
-        <v>215.5695164194086</v>
+        <v>215.56951641940859</v>
       </c>
       <c r="G27">
         <v>101.7641576046156</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4234,19 +5813,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D28">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E28">
         <v>112.8111831820431</v>
       </c>
       <c r="F28">
-        <v>228.2081528017131</v>
+        <v>228.20815280171311</v>
       </c>
       <c r="G28">
         <v>106.0685424949238</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -4254,22 +5833,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>25.09083264970256</v>
+        <v>25.090832649702559</v>
       </c>
       <c r="D29">
-        <v>51.29784446040809</v>
+        <v>51.297844460408093</v>
       </c>
       <c r="E29">
-        <v>103.0994555670134</v>
+        <v>103.09945556701339</v>
       </c>
       <c r="F29">
-        <v>204.9948409258163</v>
+        <v>204.99484092581631</v>
       </c>
       <c r="G29">
-        <v>96.12074340073509</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>96.120743400735094</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -4277,22 +5856,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>27.59660954417079</v>
+        <v>27.596609544170789</v>
       </c>
       <c r="D30">
         <v>55.76995750265435</v>
       </c>
       <c r="E30">
-        <v>113.9009517738264</v>
+        <v>113.90095177382641</v>
       </c>
       <c r="F30">
-        <v>227.911469086505</v>
+        <v>227.91146908650501</v>
       </c>
       <c r="G30">
         <v>106.2947469767891</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -4300,22 +5879,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>28.09366837409481</v>
+        <v>28.093668374094811</v>
       </c>
       <c r="D31">
-        <v>55.75416984851405</v>
+        <v>55.754169848514053</v>
       </c>
       <c r="E31">
         <v>111.1331825706034</v>
       </c>
       <c r="F31">
-        <v>221.7764458320694</v>
+        <v>221.77644583206941</v>
       </c>
       <c r="G31">
         <v>104.1893666563204</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4326,19 +5905,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D32">
-        <v>57.35533905932739</v>
+        <v>57.355339059327392</v>
       </c>
       <c r="E32">
         <v>117.1543289325507</v>
       </c>
       <c r="F32">
-        <v>232.7523086789974</v>
+        <v>232.75230867899739</v>
       </c>
       <c r="G32">
         <v>108.7045814642449</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4346,22 +5925,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>25.02260056222932</v>
+        <v>25.022600562229321</v>
       </c>
       <c r="D33">
-        <v>50.84522608762971</v>
+        <v>50.845226087629712</v>
       </c>
       <c r="E33">
-        <v>104.2952231567888</v>
+        <v>104.29522315678879</v>
       </c>
       <c r="F33">
-        <v>208.2523221830841</v>
+        <v>208.25232218308409</v>
       </c>
       <c r="G33">
-        <v>97.10384299743299</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>97.103842997432992</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4372,19 +5951,19 @@
         <v>32.97056274847715</v>
       </c>
       <c r="D34">
-        <v>65.11269837220809</v>
+        <v>65.112698372208087</v>
       </c>
       <c r="E34">
         <v>132.2253967444162</v>
       </c>
       <c r="F34">
-        <v>266.4507934888323</v>
+        <v>266.45079348883229</v>
       </c>
       <c r="G34">
-        <v>124.1898628384834</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>124.18986283848341</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4395,19 +5974,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D35">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E35">
         <v>111.9827560572969</v>
       </c>
       <c r="F35">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G35">
         <v>104.9472221513642</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4415,22 +5994,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>25.06177259678004</v>
+        <v>25.061772596780042</v>
       </c>
       <c r="D36">
-        <v>50.78798902674716</v>
+        <v>50.787989026747162</v>
       </c>
       <c r="E36">
-        <v>102.3440997142822</v>
+        <v>102.34409971428219</v>
       </c>
       <c r="F36">
         <v>205.5007992866575</v>
       </c>
       <c r="G36">
-        <v>95.92366515611673</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>95.923665156116726</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4441,19 +6020,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D37">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E37">
         <v>111.9827560572969</v>
       </c>
       <c r="F37">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G37">
-        <v>104.0330085889911</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>104.03300858899109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4461,22 +6040,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>27.20005801635743</v>
+        <v>27.200058016357431</v>
       </c>
       <c r="D38">
         <v>54.98590247034177</v>
       </c>
       <c r="E38">
-        <v>110.5575913783105</v>
+        <v>110.55759137831051</v>
       </c>
       <c r="F38">
-        <v>221.7009691942478</v>
+        <v>221.70096919424779</v>
       </c>
       <c r="G38">
-        <v>103.6111302648144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>103.61113026481441</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4487,19 +6066,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D39">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E39">
         <v>111.9827560572969</v>
       </c>
       <c r="F39">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G39">
         <v>104.9472221513642</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4510,19 +6089,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D40">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E40">
         <v>111.9827560572969</v>
       </c>
       <c r="F40">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G40">
         <v>104.9472221513642</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4530,10 +6109,10 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>24.95741732923815</v>
+        <v>24.957417329238151</v>
       </c>
       <c r="D41">
-        <v>52.5006210961032</v>
+        <v>52.500621096103202</v>
       </c>
       <c r="E41">
         <v>106.4154557545795</v>
@@ -4542,10 +6121,10 @@
         <v>214.2451250715321</v>
       </c>
       <c r="G41">
-        <v>99.52965481286324</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>99.529654812863242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -4553,22 +6132,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D42">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E42">
         <v>111.9827560572969</v>
       </c>
       <c r="F42">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G42">
         <v>104.3865619795843</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4576,22 +6155,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>24.95741732923815</v>
+        <v>24.957417329238151</v>
       </c>
       <c r="D43">
         <v>54.98590247034177</v>
       </c>
       <c r="E43">
-        <v>110.5575913783105</v>
+        <v>110.55759137831051</v>
       </c>
       <c r="F43">
-        <v>221.7009691942478</v>
+        <v>221.70096919424779</v>
       </c>
       <c r="G43">
-        <v>103.0504700930345</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>103.05047009303451</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4599,22 +6178,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>27.7300248646352</v>
+        <v>27.730024864635201</v>
       </c>
       <c r="D44">
-        <v>55.73392301975998</v>
+        <v>55.733923019759978</v>
       </c>
       <c r="E44">
         <v>113.8562961127611</v>
       </c>
       <c r="F44">
-        <v>225.7169946762131</v>
+        <v>225.71699467621309</v>
       </c>
       <c r="G44">
         <v>105.7593096683424</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4625,19 +6204,19 @@
         <v>27.33347333682185</v>
       </c>
       <c r="D45">
-        <v>55.03558274568525</v>
+        <v>55.035582745685247</v>
       </c>
       <c r="E45">
         <v>110.4067858133953</v>
       </c>
       <c r="F45">
-        <v>219.5819714217776</v>
+        <v>219.58197142177761</v>
       </c>
       <c r="G45">
         <v>103.08945332942</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4648,19 +6227,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D46">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E46">
         <v>111.9827560572969</v>
       </c>
       <c r="F46">
-        <v>225.7228714274746</v>
+        <v>225.72287142747459</v>
       </c>
       <c r="G46">
-        <v>105.2401153701776</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>105.24011537017761</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4674,16 +6253,16 @@
         <v>54.69243699517763</v>
       </c>
       <c r="E47">
-        <v>109.4612036670544</v>
+        <v>109.46120366705441</v>
       </c>
       <c r="F47">
-        <v>215.5695164194086</v>
+        <v>215.56951641940859</v>
       </c>
       <c r="G47">
         <v>101.7641576046156</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -4694,19 +6273,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D48">
-        <v>56.22361021870229</v>
+        <v>56.223610218702291</v>
       </c>
       <c r="E48">
-        <v>111.6626726298638</v>
+        <v>111.66267262986381</v>
       </c>
       <c r="F48">
-        <v>221.7764458320694</v>
+        <v>221.77644583206941</v>
       </c>
       <c r="G48">
         <v>104.3047694666849</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -4717,19 +6296,19 @@
         <v>30.97056274847715</v>
       </c>
       <c r="D49">
-        <v>56.31376433994424</v>
+        <v>56.313764339944242</v>
       </c>
       <c r="E49">
-        <v>114.2596075487725</v>
+        <v>114.25960754877249</v>
       </c>
       <c r="F49">
-        <v>230.3712106408483</v>
+        <v>230.37121064084829</v>
       </c>
       <c r="G49">
         <v>107.9787863195105</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -4740,19 +6319,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D50">
-        <v>71.9411254969543</v>
+        <v>71.941125496954299</v>
       </c>
       <c r="E50">
         <v>111.9827560572969</v>
       </c>
       <c r="F50">
-        <v>271.9655121145938</v>
+        <v>271.96551211459382</v>
       </c>
       <c r="G50">
-        <v>120.8614357137373</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>120.86143571373729</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -4763,19 +6342,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D51">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E51">
         <v>111.9827560572969</v>
       </c>
       <c r="F51">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G51">
         <v>104.9472221513642</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -4786,19 +6365,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D52">
-        <v>55.32963226464916</v>
+        <v>55.329632264649163</v>
       </c>
       <c r="E52">
-        <v>110.934942379664</v>
+        <v>110.93494237966399</v>
       </c>
       <c r="F52">
-        <v>222.1702210976759</v>
+        <v>222.17022109767589</v>
       </c>
       <c r="G52">
         <v>103.9977862320233</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -4809,19 +6388,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D53">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E53">
         <v>111.9827560572969</v>
       </c>
       <c r="F53">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G53">
         <v>104.9472221513642</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -4832,10 +6411,10 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D54">
-        <v>50.78798902674716</v>
+        <v>50.787989026747162</v>
       </c>
       <c r="E54">
-        <v>110.934942379664</v>
+        <v>110.93494237966399</v>
       </c>
       <c r="F54">
         <v>220.0512233252056</v>
@@ -4844,7 +6423,7 @@
         <v>102.3326259794302</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -4852,22 +6431,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>27.20005801635743</v>
+        <v>27.200058016357431</v>
       </c>
       <c r="D55">
         <v>54.98590247034177</v>
       </c>
       <c r="E55">
-        <v>110.5575913783105</v>
+        <v>110.55759137831051</v>
       </c>
       <c r="F55">
-        <v>221.7009691942478</v>
+        <v>221.70096919424779</v>
       </c>
       <c r="G55">
-        <v>103.6111302648144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>103.61113026481441</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -4875,22 +6454,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>27.20005801635743</v>
+        <v>27.200058016357431</v>
       </c>
       <c r="D56">
         <v>54.98590247034177</v>
       </c>
       <c r="E56">
-        <v>110.5575913783105</v>
+        <v>110.55759137831051</v>
       </c>
       <c r="F56">
-        <v>221.7009691942478</v>
+        <v>221.70096919424779</v>
       </c>
       <c r="G56">
-        <v>103.6111302648144</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>103.61113026481441</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -4901,19 +6480,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D57">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E57">
         <v>111.9827560572969</v>
       </c>
       <c r="F57">
-        <v>224.5512985522207</v>
+        <v>224.55129855222069</v>
       </c>
       <c r="G57">
         <v>104.9472221513642</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -4921,22 +6500,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>24.95741732923815</v>
+        <v>24.957417329238151</v>
       </c>
       <c r="D58">
         <v>54.98590247034177</v>
       </c>
       <c r="E58">
-        <v>110.5575913783105</v>
+        <v>110.55759137831051</v>
       </c>
       <c r="F58">
-        <v>221.7009691942478</v>
+        <v>221.70096919424779</v>
       </c>
       <c r="G58">
-        <v>103.0504700930345</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>103.05047009303451</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -4947,19 +6526,19 @@
         <v>27.33347333682185</v>
       </c>
       <c r="D59">
-        <v>55.03558274568525</v>
+        <v>55.035582745685247</v>
       </c>
       <c r="E59">
         <v>110.4067858133953</v>
       </c>
       <c r="F59">
-        <v>219.5819714217776</v>
+        <v>219.58197142177761</v>
       </c>
       <c r="G59">
         <v>103.08945332942</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -4970,19 +6549,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D60">
-        <v>68.70406320610682</v>
+        <v>68.704063206106824</v>
       </c>
       <c r="E60">
-        <v>110.934942379664</v>
+        <v>110.93494237966399</v>
       </c>
       <c r="F60">
-        <v>237.2555711660056</v>
+        <v>237.25557116600561</v>
       </c>
       <c r="G60">
         <v>111.1127314844701</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -4993,19 +6572,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D61">
-        <v>55.32963226464916</v>
+        <v>55.329632264649163</v>
       </c>
       <c r="E61">
-        <v>110.934942379664</v>
+        <v>110.93494237966399</v>
       </c>
       <c r="F61">
-        <v>222.1702210976759</v>
+        <v>222.17022109767589</v>
       </c>
       <c r="G61">
         <v>103.9977862320233</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5016,19 +6595,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D62">
-        <v>55.69848480983499</v>
+        <v>55.698484809834987</v>
       </c>
       <c r="E62">
         <v>111.9827560572969</v>
       </c>
       <c r="F62">
-        <v>255.9655121145938</v>
+        <v>255.96551211459379</v>
       </c>
       <c r="G62">
-        <v>112.8007755419574</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>112.80077554195741</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5039,19 +6618,19 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D63">
-        <v>55.32963226464916</v>
+        <v>55.329632264649163</v>
       </c>
       <c r="E63">
-        <v>110.934942379664</v>
+        <v>110.93494237966399</v>
       </c>
       <c r="F63">
         <v>220.0512233252056</v>
       </c>
       <c r="G63">
-        <v>103.4680367889057</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>103.46803678890571</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5059,22 +6638,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>27.20005801635743</v>
+        <v>27.200058016357431</v>
       </c>
       <c r="D64">
         <v>54.98590247034177</v>
       </c>
       <c r="E64">
-        <v>110.5575913783105</v>
+        <v>110.55759137831051</v>
       </c>
       <c r="F64">
-        <v>221.7009691942478</v>
+        <v>221.70096919424779</v>
       </c>
       <c r="G64">
-        <v>103.6111302648144</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>103.61113026481441</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -5085,16 +6664,16 @@
         <v>27.55634918610405</v>
       </c>
       <c r="D65">
-        <v>55.32963226464916</v>
+        <v>55.329632264649163</v>
       </c>
       <c r="E65">
-        <v>110.934942379664</v>
+        <v>110.93494237966399</v>
       </c>
       <c r="F65">
-        <v>237.2014406395573</v>
+        <v>237.20144063955729</v>
       </c>
       <c r="G65">
-        <v>107.7555911174936</v>
+        <v>107.75559111749359</v>
       </c>
     </row>
   </sheetData>
@@ -5103,11 +6682,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5130,7 +6709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5153,7 +6732,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5176,7 +6755,7 @@
         <v>254.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5199,7 +6778,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5222,7 +6801,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5245,7 +6824,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5268,7 +6847,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5291,7 +6870,7 @@
         <v>167.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5314,7 +6893,7 @@
         <v>234.25</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5337,7 +6916,7 @@
         <v>165.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5360,7 +6939,7 @@
         <v>254.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5383,7 +6962,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5406,7 +6985,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5429,7 +7008,7 @@
         <v>254.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5452,7 +7031,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5475,7 +7054,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5498,7 +7077,7 @@
         <v>163.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5521,7 +7100,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5544,7 +7123,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5567,7 +7146,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5590,7 +7169,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5613,7 +7192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -5636,7 +7215,7 @@
         <v>167.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5659,7 +7238,7 @@
         <v>234.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5682,7 +7261,7 @@
         <v>211.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -5705,7 +7284,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -5728,7 +7307,7 @@
         <v>165.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -5751,7 +7330,7 @@
         <v>185.25</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5774,7 +7353,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5797,7 +7376,7 @@
         <v>254.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5820,7 +7399,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5843,7 +7422,7 @@
         <v>205.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5866,7 +7445,7 @@
         <v>163.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5889,7 +7468,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5912,7 +7491,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5935,7 +7514,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5958,7 +7537,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5981,7 +7560,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -6004,7 +7583,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -6027,7 +7606,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -6050,7 +7629,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -6073,7 +7652,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -6096,7 +7675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6119,7 +7698,7 @@
         <v>211.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6142,7 +7721,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6165,7 +7744,7 @@
         <v>195.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6188,7 +7767,7 @@
         <v>185.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -6211,7 +7790,7 @@
         <v>205.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -6234,7 +7813,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -6257,7 +7836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -6280,7 +7859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -6303,7 +7882,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -6326,7 +7905,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -6349,7 +7928,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -6372,7 +7951,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -6395,7 +7974,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -6418,7 +7997,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -6441,7 +8020,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -6464,7 +8043,7 @@
         <v>195.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -6487,7 +8066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -6510,7 +8089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -6533,7 +8112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -6556,7 +8135,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -6579,7 +8158,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -6608,11 +8187,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6635,7 +8214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6658,7 +8237,7 @@
         <v>1988.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6681,7 +8260,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6704,7 +8283,7 @@
         <v>857.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6727,7 +8306,7 @@
         <v>1486.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6750,7 +8329,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6773,7 +8352,7 @@
         <v>1988.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6796,7 +8375,7 @@
         <v>2009.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6819,7 +8398,7 @@
         <v>835.25</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6842,7 +8421,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6865,7 +8444,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6888,7 +8467,7 @@
         <v>1409.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6911,7 +8490,7 @@
         <v>857.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6934,7 +8513,7 @@
         <v>933.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6957,7 +8536,7 @@
         <v>984.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6980,7 +8559,7 @@
         <v>1486.75</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7003,7 +8582,7 @@
         <v>1494.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7026,7 +8605,7 @@
         <v>42.25</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7049,7 +8628,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7072,7 +8651,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7095,7 +8674,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7118,7 +8697,7 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -7141,7 +8720,7 @@
         <v>2009.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7164,7 +8743,7 @@
         <v>835.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7187,7 +8766,7 @@
         <v>870.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7210,7 +8789,7 @@
         <v>729.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7233,7 +8812,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7256,7 +8835,7 @@
         <v>1078.25</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7279,7 +8858,7 @@
         <v>1409.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7302,7 +8881,7 @@
         <v>933.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7325,7 +8904,7 @@
         <v>984.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7348,7 +8927,7 @@
         <v>984.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7371,7 +8950,7 @@
         <v>1494.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7394,7 +8973,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7417,7 +8996,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7440,7 +9019,7 @@
         <v>42.25</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7463,7 +9042,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7486,7 +9065,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -7509,7 +9088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -7532,7 +9111,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -7555,7 +9134,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -7578,7 +9157,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -7601,7 +9180,7 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7624,7 +9203,7 @@
         <v>870.5</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7647,7 +9226,7 @@
         <v>729.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7670,7 +9249,7 @@
         <v>729.25</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7693,7 +9272,7 @@
         <v>1078.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -7716,7 +9295,7 @@
         <v>984.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -7739,7 +9318,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -7762,7 +9341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -7785,7 +9364,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -7808,7 +9387,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -7831,7 +9410,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -7854,7 +9433,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -7877,7 +9456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -7900,7 +9479,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -7923,7 +9502,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -7946,7 +9525,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -7969,7 +9548,7 @@
         <v>729.25</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -7992,7 +9571,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -8015,7 +9594,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -8038,7 +9617,7 @@
         <v>26.25</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -8061,7 +9640,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -8084,7 +9663,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -8113,11 +9692,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8140,7 +9719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8163,7 +9742,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8186,7 +9765,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8209,7 +9788,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8232,7 +9811,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8255,7 +9834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8278,7 +9857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8301,7 +9880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8324,7 +9903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8347,7 +9926,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8370,7 +9949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8393,7 +9972,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8416,7 +9995,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8439,7 +10018,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8462,7 +10041,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8485,7 +10064,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8508,7 +10087,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8531,7 +10110,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8554,7 +10133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8577,7 +10156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8600,7 +10179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8623,7 +10202,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -8646,7 +10225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8669,7 +10248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8692,7 +10271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8715,7 +10294,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8738,7 +10317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8761,7 +10340,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8784,7 +10363,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8807,7 +10386,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8830,7 +10409,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8853,7 +10432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8876,7 +10455,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8899,7 +10478,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8922,7 +10501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8945,7 +10524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8968,7 +10547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8991,7 +10570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -9014,7 +10593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -9037,7 +10616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -9060,7 +10639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -9083,7 +10662,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -9106,7 +10685,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -9129,7 +10708,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -9152,7 +10731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -9175,7 +10754,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -9198,7 +10777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -9221,7 +10800,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -9244,7 +10823,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -9267,7 +10846,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -9290,7 +10869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -9313,7 +10892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -9336,7 +10915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -9359,7 +10938,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -9382,7 +10961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -9405,7 +10984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -9428,7 +11007,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -9451,7 +11030,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -9474,7 +11053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -9497,7 +11076,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -9520,7 +11099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -9543,7 +11122,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -9566,7 +11145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -9589,7 +11168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_128_avg_length.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02167198-6D40-4C51-8660-26D62F40B47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -195,8 +189,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,1540 +253,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>A*</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.6979999999999993E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.4133000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.4183199999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1549548</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7095-400C-A049-4EAF6F7D294B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BDS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2.5099999999999998E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1527E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.5894000000000004E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.9486199999999999E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7095-400C-A049-4EAF6F7D294B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BRC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.9189999999999998E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2819999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.1022000000000012E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.3330100000000001E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7095-400C-A049-4EAF6F7D294B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>GL</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.3849999999999988E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.8538999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.2092500000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.2750199999999996E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7095-400C-A049-4EAF6F7D294B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>JPS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.3520000000000002E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.114E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.540300000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.4596899999999999E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-7095-400C-A049-4EAF6F7D294B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PPO</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.9719999999999994E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.5000999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.3267900000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1566158</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-7095-400C-A049-4EAF6F7D294B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TPF</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5.3450000000000004E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.2770999999999998E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.17194E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14819570000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-7095-400C-A049-4EAF6F7D294B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:hiLowLines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:hiLowLines>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="693588143"/>
-        <c:axId val="693588623"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="693588143"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693588623"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="693588623"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693588143"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="id-ID"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E557BFFA-7967-D2D5-AE8E-73E4A078FFF5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Red Orange">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1800,37 +267,37 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="505046"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="E84C22"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="FFBD47"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="B64926"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FF8427"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="B22600"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="666699"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1864,7 +331,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1899,10 +365,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2075,11 +540,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2110,22 +575,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4.6979999999999993E-4</v>
+        <v>0.0004728000000000001</v>
       </c>
       <c r="D2">
-        <v>3.4133000000000002E-3</v>
+        <v>0.0033926</v>
       </c>
       <c r="E2">
-        <v>2.4183199999999998E-2</v>
+        <v>0.0243116</v>
       </c>
       <c r="F2">
-        <v>0.1549548</v>
+        <v>0.1533175</v>
       </c>
       <c r="G2">
-        <v>4.5755274999999998E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.04537362500000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2133,22 +598,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2.5099999999999998E-4</v>
+        <v>0.0002677</v>
       </c>
       <c r="D3">
-        <v>1.1527E-3</v>
+        <v>0.001075</v>
       </c>
       <c r="E3">
-        <v>4.5894000000000004E-3</v>
+        <v>0.004739999999999999</v>
       </c>
       <c r="F3">
-        <v>1.9486199999999999E-2</v>
+        <v>0.0196129</v>
       </c>
       <c r="G3">
-        <v>6.3698250000000008E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006423900000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2156,22 +621,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>3.9189999999999998E-4</v>
+        <v>0.0004341999999999999</v>
       </c>
       <c r="D4">
-        <v>1.2819999999999999E-3</v>
+        <v>0.0012278</v>
       </c>
       <c r="E4">
-        <v>5.1022000000000012E-3</v>
+        <v>0.005261200000000001</v>
       </c>
       <c r="F4">
-        <v>3.3330100000000001E-2</v>
+        <v>0.0333408</v>
       </c>
       <c r="G4">
-        <v>1.002655E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.010066</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2179,22 +644,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>3.3849999999999988E-4</v>
+        <v>0.000336</v>
       </c>
       <c r="D5">
-        <v>1.8538999999999999E-3</v>
+        <v>0.001818</v>
       </c>
       <c r="E5">
-        <v>1.2092500000000001E-2</v>
+        <v>0.0123613</v>
       </c>
       <c r="F5">
-        <v>8.2750199999999996E-2</v>
+        <v>0.08410869999999999</v>
       </c>
       <c r="G5">
-        <v>2.4258775E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.024656</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2202,22 +667,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>3.3520000000000002E-4</v>
+        <v>0.0003419</v>
       </c>
       <c r="D6">
-        <v>1.114E-3</v>
+        <v>0.0010717</v>
       </c>
       <c r="E6">
-        <v>3.540300000000001E-3</v>
+        <v>0.0034443</v>
       </c>
       <c r="F6">
-        <v>1.4596899999999999E-2</v>
+        <v>0.014533</v>
       </c>
       <c r="G6">
-        <v>4.8966000000000001E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004847725</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2225,22 +690,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>4.9719999999999994E-4</v>
+        <v>0.0005167</v>
       </c>
       <c r="D7">
-        <v>3.5000999999999999E-3</v>
+        <v>0.0034616</v>
       </c>
       <c r="E7">
-        <v>2.3267900000000001E-2</v>
+        <v>0.0235942</v>
       </c>
       <c r="F7">
-        <v>0.1566158</v>
+        <v>0.1550685</v>
       </c>
       <c r="G7">
-        <v>4.5970249999999997E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.04566025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2248,22 +713,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>5.3450000000000004E-4</v>
+        <v>0.0005405000000000001</v>
       </c>
       <c r="D8">
-        <v>3.2770999999999998E-3</v>
+        <v>0.003384</v>
       </c>
       <c r="E8">
-        <v>2.17194E-2</v>
+        <v>0.021159</v>
       </c>
       <c r="F8">
-        <v>0.14819570000000001</v>
+        <v>0.1469438</v>
       </c>
       <c r="G8">
-        <v>4.3431675000000003E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.04300682500000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2271,22 +736,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>4.0809999999999989E-4</v>
+        <v>0.0004372</v>
       </c>
       <c r="D9">
-        <v>1.1058000000000001E-3</v>
+        <v>0.0011649</v>
       </c>
       <c r="E9">
-        <v>3.4973000000000001E-3</v>
+        <v>0.0035734</v>
       </c>
       <c r="F9">
-        <v>1.3848600000000001E-2</v>
+        <v>0.0143742</v>
       </c>
       <c r="G9">
-        <v>4.7149499999999999E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004887424999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2294,22 +759,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>2.6160000000000002E-4</v>
+        <v>0.0002648</v>
       </c>
       <c r="D10">
-        <v>1.3025999999999999E-3</v>
+        <v>0.00127</v>
       </c>
       <c r="E10">
-        <v>6.1658000000000008E-3</v>
+        <v>0.005435600000000001</v>
       </c>
       <c r="F10">
-        <v>2.2590800000000001E-2</v>
+        <v>0.0237309</v>
       </c>
       <c r="G10">
-        <v>7.5801999999999996E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007675325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2317,22 +782,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>2.72E-4</v>
+        <v>0.0002964</v>
       </c>
       <c r="D11">
-        <v>1.2396E-3</v>
+        <v>0.0011845</v>
       </c>
       <c r="E11">
-        <v>5.0239000000000004E-3</v>
+        <v>0.005312600000000001</v>
       </c>
       <c r="F11">
-        <v>2.0179900000000001E-2</v>
+        <v>0.0204989</v>
       </c>
       <c r="G11">
-        <v>6.6788500000000001E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006823099999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2340,22 +805,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>3.7540000000000002E-4</v>
+        <v>0.0003654</v>
       </c>
       <c r="D12">
-        <v>1.2882E-3</v>
+        <v>0.0013404</v>
       </c>
       <c r="E12">
-        <v>4.836E-3</v>
+        <v>0.0051806</v>
       </c>
       <c r="F12">
-        <v>2.0947899999999998E-2</v>
+        <v>0.0210455</v>
       </c>
       <c r="G12">
-        <v>6.8618750000000008E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006982975000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2363,22 +828,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>4.326E-4</v>
+        <v>0.0004697</v>
       </c>
       <c r="D13">
-        <v>1.407E-3</v>
+        <v>0.0013949</v>
       </c>
       <c r="E13">
-        <v>5.4511999999999998E-3</v>
+        <v>0.0054372</v>
       </c>
       <c r="F13">
-        <v>3.4081599999999997E-2</v>
+        <v>0.0344881</v>
       </c>
       <c r="G13">
-        <v>1.0343099999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.010447475</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2386,22 +851,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>4.2890000000000002E-4</v>
+        <v>0.0004332</v>
       </c>
       <c r="D14">
-        <v>1.4438999999999999E-3</v>
+        <v>0.0013609</v>
       </c>
       <c r="E14">
-        <v>5.3214999999999998E-3</v>
+        <v>0.005377900000000001</v>
       </c>
       <c r="F14">
-        <v>3.3543700000000003E-2</v>
+        <v>0.0336322</v>
       </c>
       <c r="G14">
-        <v>1.0184500000000001E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01020105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2409,22 +874,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>4.3899999999999999E-4</v>
+        <v>0.000452</v>
       </c>
       <c r="D15">
-        <v>1.5589E-3</v>
+        <v>0.0015496</v>
       </c>
       <c r="E15">
-        <v>7.3253000000000016E-3</v>
+        <v>0.007758100000000001</v>
       </c>
       <c r="F15">
-        <v>5.39783E-2</v>
+        <v>0.0543739</v>
       </c>
       <c r="G15">
-        <v>1.5825374999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0160334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2432,22 +897,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>3.4820000000000001E-4</v>
+        <v>0.000396</v>
       </c>
       <c r="D16">
-        <v>1.9375E-3</v>
+        <v>0.0018635</v>
       </c>
       <c r="E16">
-        <v>1.24174E-2</v>
+        <v>0.0128628</v>
       </c>
       <c r="F16">
-        <v>8.3875199999999997E-2</v>
+        <v>0.0843817</v>
       </c>
       <c r="G16">
-        <v>2.4644574999999998E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.024876</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2455,22 +920,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>3.9849999999999998E-4</v>
+        <v>0.0003903</v>
       </c>
       <c r="D17">
-        <v>2.0178000000000001E-3</v>
+        <v>0.0019761</v>
       </c>
       <c r="E17">
-        <v>1.2499700000000001E-2</v>
+        <v>0.0128464</v>
       </c>
       <c r="F17">
-        <v>8.6779399999999993E-2</v>
+        <v>0.08683779999999999</v>
       </c>
       <c r="G17">
-        <v>2.5423850000000001E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02551265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2478,22 +943,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>4.035000000000001E-4</v>
+        <v>0.0003553</v>
       </c>
       <c r="D18">
-        <v>1.2983000000000001E-3</v>
+        <v>0.0013034</v>
       </c>
       <c r="E18">
-        <v>4.2475000000000004E-3</v>
+        <v>0.004232700000000001</v>
       </c>
       <c r="F18">
-        <v>1.6243799999999999E-2</v>
+        <v>0.0161375</v>
       </c>
       <c r="G18">
-        <v>5.5482749999999992E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005507225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2501,22 +966,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3.0219999999999997E-4</v>
+        <v>0.0003093</v>
       </c>
       <c r="D19">
-        <v>7.5450000000000007E-4</v>
+        <v>0.0007317</v>
       </c>
       <c r="E19">
-        <v>2.1316999999999998E-3</v>
+        <v>0.0021409</v>
       </c>
       <c r="F19">
-        <v>8.1196000000000011E-3</v>
+        <v>0.0079796</v>
       </c>
       <c r="G19">
-        <v>2.827000000000001E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.002790375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2524,22 +989,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>3.2969999999999988E-4</v>
+        <v>0.0003399</v>
       </c>
       <c r="D20">
-        <v>1.1217E-3</v>
+        <v>0.0010698</v>
       </c>
       <c r="E20">
-        <v>3.7222000000000002E-3</v>
+        <v>0.0036075</v>
       </c>
       <c r="F20">
-        <v>1.39823E-2</v>
+        <v>0.0139827</v>
       </c>
       <c r="G20">
-        <v>4.788975E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004749975</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2547,22 +1012,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>3.7990000000000002E-4</v>
+        <v>0.0003733</v>
       </c>
       <c r="D21">
-        <v>1.1555000000000001E-3</v>
+        <v>0.0011537</v>
       </c>
       <c r="E21">
-        <v>3.6817E-3</v>
+        <v>0.0036317</v>
       </c>
       <c r="F21">
-        <v>1.5166799999999999E-2</v>
+        <v>0.0146075</v>
       </c>
       <c r="G21">
-        <v>5.0959750000000009E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004941549999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2570,22 +1035,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>5.6349999999999998E-4</v>
+        <v>0.0005975</v>
       </c>
       <c r="D22">
-        <v>3.4185000000000001E-3</v>
+        <v>0.0034817</v>
       </c>
       <c r="E22">
-        <v>2.07449E-2</v>
+        <v>0.0215055</v>
       </c>
       <c r="F22">
-        <v>0.1504376</v>
+        <v>0.1479387</v>
       </c>
       <c r="G22">
-        <v>4.3791124999999993E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.04338085</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2593,22 +1058,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>4.7830000000000003E-4</v>
+        <v>0.0004371000000000001</v>
       </c>
       <c r="D23">
-        <v>1.2669000000000001E-3</v>
+        <v>0.0012484</v>
       </c>
       <c r="E23">
-        <v>3.7813E-3</v>
+        <v>0.003917700000000001</v>
       </c>
       <c r="F23">
-        <v>1.5398200000000001E-2</v>
+        <v>0.0155522</v>
       </c>
       <c r="G23">
-        <v>5.2311749999999994E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005288849999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2616,22 +1081,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>4.2450000000000013E-4</v>
+        <v>0.0004544999999999999</v>
       </c>
       <c r="D24">
-        <v>1.3037000000000001E-3</v>
+        <v>0.0012833</v>
       </c>
       <c r="E24">
-        <v>3.7395000000000002E-3</v>
+        <v>0.0038987</v>
       </c>
       <c r="F24">
-        <v>1.4630499999999999E-2</v>
+        <v>0.0150326</v>
       </c>
       <c r="G24">
-        <v>5.02455E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005167275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2639,22 +1104,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>4.3689999999999989E-4</v>
+        <v>0.0004444</v>
       </c>
       <c r="D25">
-        <v>1.4468E-3</v>
+        <v>0.0014708</v>
       </c>
       <c r="E25">
-        <v>5.5265999999999996E-3</v>
+        <v>0.005525</v>
       </c>
       <c r="F25">
-        <v>3.1122400000000001E-2</v>
+        <v>0.0312953</v>
       </c>
       <c r="G25">
-        <v>9.6331750000000008E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009683875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2662,22 +1127,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>2.9770000000000003E-4</v>
+        <v>0.0003178</v>
       </c>
       <c r="D26">
-        <v>1.3485000000000001E-3</v>
+        <v>0.0013661</v>
       </c>
       <c r="E26">
-        <v>5.5541999999999996E-3</v>
+        <v>0.005550100000000001</v>
       </c>
       <c r="F26">
-        <v>2.3655599999999999E-2</v>
+        <v>0.0241186</v>
       </c>
       <c r="G26">
-        <v>7.7140000000000004E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00783815</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2685,22 +1150,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>3.0590000000000001E-4</v>
+        <v>0.0003256</v>
       </c>
       <c r="D27">
-        <v>1.4496999999999999E-3</v>
+        <v>0.0014133</v>
       </c>
       <c r="E27">
-        <v>5.5568000000000006E-3</v>
+        <v>0.0058844</v>
       </c>
       <c r="F27">
-        <v>2.3602499999999998E-2</v>
+        <v>0.0243327</v>
       </c>
       <c r="G27">
-        <v>7.7287249999999997E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2708,22 +1173,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>3.813E-4</v>
+        <v>0.0003943999999999999</v>
       </c>
       <c r="D28">
-        <v>1.3868000000000001E-3</v>
+        <v>0.0013837</v>
       </c>
       <c r="E28">
-        <v>5.1884000000000001E-3</v>
+        <v>0.005332000000000001</v>
       </c>
       <c r="F28">
-        <v>2.2164300000000001E-2</v>
+        <v>0.0225725</v>
       </c>
       <c r="G28">
-        <v>7.2801999999999997E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007420650000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2731,22 +1196,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>4.5359999999999991E-4</v>
+        <v>0.0004965</v>
       </c>
       <c r="D29">
-        <v>1.5414999999999999E-3</v>
+        <v>0.0014839</v>
       </c>
       <c r="E29">
-        <v>5.5545000000000004E-3</v>
+        <v>0.0057586</v>
       </c>
       <c r="F29">
-        <v>3.4673200000000001E-2</v>
+        <v>0.0348707</v>
       </c>
       <c r="G29">
-        <v>1.0555699999999999E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.010652425</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2754,22 +1219,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>4.8289999999999997E-4</v>
+        <v>0.0005207999999999999</v>
       </c>
       <c r="D30">
-        <v>1.7673999999999999E-3</v>
+        <v>0.0016484</v>
       </c>
       <c r="E30">
-        <v>7.5839000000000002E-3</v>
+        <v>0.0080012</v>
       </c>
       <c r="F30">
-        <v>5.4705400000000001E-2</v>
+        <v>0.055125</v>
       </c>
       <c r="G30">
-        <v>1.6134900000000001E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01632385</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2777,22 +1242,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>4.7659999999999988E-4</v>
+        <v>0.0004959</v>
       </c>
       <c r="D31">
-        <v>1.6291000000000001E-3</v>
+        <v>0.001631</v>
       </c>
       <c r="E31">
-        <v>6.8653000000000004E-3</v>
+        <v>0.006875399999999999</v>
       </c>
       <c r="F31">
-        <v>4.5674300000000001E-2</v>
+        <v>0.0462979</v>
       </c>
       <c r="G31">
-        <v>1.3661325E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01382505</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2800,22 +1265,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>4.1859999999999998E-4</v>
+        <v>0.0004383</v>
       </c>
       <c r="D32">
-        <v>2.1224E-3</v>
+        <v>0.0021363</v>
       </c>
       <c r="E32">
-        <v>1.29578E-2</v>
+        <v>0.0131337</v>
       </c>
       <c r="F32">
-        <v>8.6198300000000005E-2</v>
+        <v>0.08695509999999999</v>
       </c>
       <c r="G32">
-        <v>2.5424275E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02566585</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2823,22 +1288,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>4.2620000000000001E-4</v>
+        <v>0.0004094</v>
       </c>
       <c r="D33">
-        <v>1.2626E-3</v>
+        <v>0.001201</v>
       </c>
       <c r="E33">
-        <v>4.1364000000000001E-3</v>
+        <v>0.0041211</v>
       </c>
       <c r="F33">
-        <v>1.6279999999999999E-2</v>
+        <v>0.0165208</v>
       </c>
       <c r="G33">
-        <v>5.5262999999999987E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005563075</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2846,22 +1311,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>5.0140000000000004E-4</v>
+        <v>0.0004750999999999999</v>
       </c>
       <c r="D34">
-        <v>1.8479E-3</v>
+        <v>0.0017956</v>
       </c>
       <c r="E34">
-        <v>5.9664000000000002E-3</v>
+        <v>0.0061476</v>
       </c>
       <c r="F34">
-        <v>2.55418E-2</v>
+        <v>0.0254941</v>
       </c>
       <c r="G34">
-        <v>8.4643749999999997E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008478099999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2869,22 +1334,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>4.1379999999999998E-4</v>
+        <v>0.0003983</v>
       </c>
       <c r="D35">
-        <v>1.3523000000000001E-3</v>
+        <v>0.0013616</v>
       </c>
       <c r="E35">
-        <v>4.3365999999999986E-3</v>
+        <v>0.0042896</v>
       </c>
       <c r="F35">
-        <v>1.6409199999999999E-2</v>
+        <v>0.01633109999999999</v>
       </c>
       <c r="G35">
-        <v>5.6279749999999986E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005595149999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2892,22 +1357,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>3.2729999999999999E-4</v>
+        <v>0.0003494</v>
       </c>
       <c r="D36">
-        <v>7.9600000000000005E-4</v>
+        <v>0.0007678</v>
       </c>
       <c r="E36">
-        <v>2.2005000000000002E-3</v>
+        <v>0.00223</v>
       </c>
       <c r="F36">
-        <v>8.053900000000001E-3</v>
+        <v>0.008085499999999999</v>
       </c>
       <c r="G36">
-        <v>2.8444249999999998E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.002858175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2915,22 +1380,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>3.3480000000000001E-4</v>
+        <v>0.0003444</v>
       </c>
       <c r="D37">
-        <v>8.5610000000000005E-4</v>
+        <v>0.0008087000000000001</v>
       </c>
       <c r="E37">
-        <v>2.7775E-3</v>
+        <v>0.0029497</v>
       </c>
       <c r="F37">
-        <v>1.03246E-2</v>
+        <v>0.0103515</v>
       </c>
       <c r="G37">
-        <v>3.57325E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003613575</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2938,22 +1403,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>3.8660000000000002E-4</v>
+        <v>0.0003694000000000001</v>
       </c>
       <c r="D38">
-        <v>1.1617000000000001E-3</v>
+        <v>0.001158</v>
       </c>
       <c r="E38">
-        <v>3.7334999999999998E-3</v>
+        <v>0.003830899999999999</v>
       </c>
       <c r="F38">
-        <v>1.38925E-2</v>
+        <v>0.014121</v>
       </c>
       <c r="G38">
-        <v>4.7935749999999996E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004869825</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -2961,22 +1426,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>4.8260000000000002E-4</v>
+        <v>0.0005077</v>
       </c>
       <c r="D39">
-        <v>1.4099E-3</v>
+        <v>0.0013684</v>
       </c>
       <c r="E39">
-        <v>4.0082E-3</v>
+        <v>0.0041108</v>
       </c>
       <c r="F39">
-        <v>1.585E-2</v>
+        <v>0.0166561</v>
       </c>
       <c r="G39">
-        <v>5.4376749999999986E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00566075</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -2984,22 +1449,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>4.8069999999999997E-4</v>
+        <v>0.0005022000000000001</v>
       </c>
       <c r="D40">
-        <v>1.5788E-3</v>
+        <v>0.0015881</v>
       </c>
       <c r="E40">
-        <v>5.9229E-3</v>
+        <v>0.0058801</v>
       </c>
       <c r="F40">
-        <v>3.2061899999999997E-2</v>
+        <v>0.0323983</v>
       </c>
       <c r="G40">
-        <v>1.0011074999999999E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.010092175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3007,22 +1472,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>4.7550000000000001E-4</v>
+        <v>0.0004869</v>
       </c>
       <c r="D41">
-        <v>1.5816000000000001E-3</v>
+        <v>0.0015034</v>
       </c>
       <c r="E41">
-        <v>5.1278000000000001E-3</v>
+        <v>0.0051078</v>
       </c>
       <c r="F41">
-        <v>2.5950299999999999E-2</v>
+        <v>0.0269017</v>
       </c>
       <c r="G41">
-        <v>8.2838000000000009E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008499949999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -3030,22 +1495,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>3.7270000000000001E-4</v>
+        <v>0.0003838</v>
       </c>
       <c r="D42">
-        <v>1.5120000000000001E-3</v>
+        <v>0.0015139</v>
       </c>
       <c r="E42">
-        <v>5.7991999999999991E-3</v>
+        <v>0.007221999999999999</v>
       </c>
       <c r="F42">
-        <v>2.5253500000000002E-2</v>
+        <v>0.024742</v>
       </c>
       <c r="G42">
-        <v>8.2343499999999997E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008465425</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -3053,22 +1518,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>5.3159999999999991E-4</v>
+        <v>0.0005347</v>
       </c>
       <c r="D43">
-        <v>1.6758000000000001E-3</v>
+        <v>0.0016557</v>
       </c>
       <c r="E43">
-        <v>7.1313000000000001E-3</v>
+        <v>0.0070828</v>
       </c>
       <c r="F43">
-        <v>4.7021899999999991E-2</v>
+        <v>0.04715920000000001</v>
       </c>
       <c r="G43">
-        <v>1.4090149999999999E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0141081</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3076,22 +1541,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>4.6490000000000002E-4</v>
+        <v>0.0004533</v>
       </c>
       <c r="D44">
-        <v>1.2842999999999999E-3</v>
+        <v>0.0013291</v>
       </c>
       <c r="E44">
-        <v>4.3290999999999998E-3</v>
+        <v>0.004209399999999999</v>
       </c>
       <c r="F44">
-        <v>1.6291799999999999E-2</v>
+        <v>0.0165949</v>
       </c>
       <c r="G44">
-        <v>5.5925249999999992E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005646674999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3099,22 +1564,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>4.4549999999999999E-4</v>
+        <v>0.0004353</v>
       </c>
       <c r="D45">
-        <v>1.4423000000000001E-3</v>
+        <v>0.0013372</v>
       </c>
       <c r="E45">
-        <v>4.4428999999999996E-3</v>
+        <v>0.0045466</v>
       </c>
       <c r="F45">
-        <v>1.7775599999999999E-2</v>
+        <v>0.0178145</v>
       </c>
       <c r="G45">
-        <v>6.0265749999999993E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0060334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3122,22 +1587,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>5.2859999999999995E-4</v>
+        <v>0.0005009999999999999</v>
       </c>
       <c r="D46">
-        <v>1.8963000000000001E-3</v>
+        <v>0.0018649</v>
       </c>
       <c r="E46">
-        <v>6.1558000000000003E-3</v>
+        <v>0.0061682</v>
       </c>
       <c r="F46">
-        <v>2.5393800000000001E-2</v>
+        <v>0.0260283</v>
       </c>
       <c r="G46">
-        <v>8.4936250000000012E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008640600000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3145,22 +1610,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>3.5450000000000011E-4</v>
+        <v>0.0003608</v>
       </c>
       <c r="D47">
-        <v>9.0379999999999996E-4</v>
+        <v>0.0008780999999999999</v>
       </c>
       <c r="E47">
-        <v>2.8887000000000001E-3</v>
+        <v>0.002939</v>
       </c>
       <c r="F47">
-        <v>1.0426100000000001E-2</v>
+        <v>0.0103595</v>
       </c>
       <c r="G47">
-        <v>3.6432750000000001E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00363435</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -3168,22 +1633,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>5.0960000000000003E-4</v>
+        <v>0.0005325</v>
       </c>
       <c r="D48">
-        <v>1.6523E-3</v>
+        <v>0.0016184</v>
       </c>
       <c r="E48">
-        <v>5.5521000000000008E-3</v>
+        <v>0.0055483</v>
       </c>
       <c r="F48">
-        <v>2.6772899999999999E-2</v>
+        <v>0.0271988</v>
       </c>
       <c r="G48">
-        <v>8.6217250000000002E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0087245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -3191,33 +1656,32 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>4.8509999999999992E-4</v>
+        <v>0.000456</v>
       </c>
       <c r="D49">
-        <v>1.4978000000000001E-3</v>
+        <v>0.0014813</v>
       </c>
       <c r="E49">
-        <v>4.5199000000000003E-3</v>
+        <v>0.004572</v>
       </c>
       <c r="F49">
-        <v>1.7765099999999999E-2</v>
+        <v>0.0181333</v>
       </c>
       <c r="G49">
-        <v>6.0669749999999996E-3</v>
+        <v>0.00616065</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3240,7 +1704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3263,7 +1727,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3286,7 +1750,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3309,7 +1773,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3332,7 +1796,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3355,7 +1819,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3378,7 +1842,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3401,7 +1865,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3424,7 +1888,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3447,7 +1911,7 @@
         <v>79.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3470,7 +1934,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3493,7 +1957,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3516,7 +1980,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3539,7 +2003,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3562,7 +2026,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3585,7 +2049,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3608,7 +2072,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -3631,7 +2095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -3654,7 +2118,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -3677,7 +2141,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -3700,7 +2164,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -3723,7 +2187,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -3746,7 +2210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -3769,7 +2233,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -3792,7 +2256,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -3815,7 +2279,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -3838,7 +2302,7 @@
         <v>80.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3861,7 +2325,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -3884,7 +2348,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3907,7 +2371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -3930,7 +2394,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -3953,7 +2417,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -3976,7 +2440,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -3999,7 +2463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4022,7 +2486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4045,7 +2509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4068,7 +2532,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4091,7 +2555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -4114,7 +2578,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -4137,7 +2601,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -4160,7 +2624,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -4183,7 +2647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -4206,7 +2670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4229,7 +2693,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4252,7 +2716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4275,7 +2739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4298,7 +2762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -4321,7 +2785,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -4350,11 +2814,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4377,7 +2841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4385,10 +2849,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D2">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E2">
         <v>100.8111831820431</v>
@@ -4397,10 +2861,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G2">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4408,22 +2872,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D3">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E3">
-        <v>101.63961030678929</v>
+        <v>101.6396103067893</v>
       </c>
       <c r="F3">
-        <v>203.86500705120551</v>
+        <v>203.8650070512055</v>
       </c>
       <c r="G3">
-        <v>94.836309447890187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.83630944789019</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4431,22 +2895,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D4">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E4">
         <v>102.5685424949238</v>
       </c>
       <c r="F4">
-        <v>208.30865786510151</v>
+        <v>208.3086578651015</v>
       </c>
       <c r="G4">
-        <v>96.179455198397804</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.1794551983978</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4454,10 +2918,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D5">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E5">
         <v>100.8111831820431</v>
@@ -4466,10 +2930,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G5">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4477,10 +2941,10 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D6">
-        <v>49.698484809834987</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="E6">
         <v>100.8111831820431</v>
@@ -4489,10 +2953,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G6">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4500,22 +2964,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>23.963990038857649</v>
+        <v>23.96399003885765</v>
       </c>
       <c r="D7">
-        <v>48.505708255927161</v>
+        <v>48.50570825592716</v>
       </c>
       <c r="E7">
-        <v>96.644459689168144</v>
+        <v>96.64445968916814</v>
       </c>
       <c r="F7">
         <v>197.7852523250836</v>
       </c>
       <c r="G7">
-        <v>91.724852577259156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>91.72485257725916</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4523,10 +2987,10 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D8">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E8">
         <v>100.8111831820431</v>
@@ -4535,10 +2999,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G8">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -4546,22 +3010,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D9">
-        <v>50.526911934581179</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="E9">
         <v>103.39696961967</v>
       </c>
       <c r="F9">
-        <v>210.79393923934001</v>
+        <v>210.79393923934</v>
       </c>
       <c r="G9">
-        <v>97.214989104330527</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.21498910433053</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4569,22 +3033,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>24.727922061357852</v>
+        <v>24.72792206135785</v>
       </c>
       <c r="D10">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E10">
         <v>100.8111831820431</v>
       </c>
       <c r="F10">
-        <v>204.79393923934001</v>
+        <v>204.79393923934</v>
       </c>
       <c r="G10">
-        <v>95.007882323143988</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.00788232314399</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4592,22 +3056,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>23.785844453984339</v>
+        <v>23.78584445398434</v>
       </c>
       <c r="D11">
-        <v>48.141594936500709</v>
+        <v>48.14159493650071</v>
       </c>
       <c r="E11">
-        <v>95.735027243962222</v>
+        <v>95.73502724396222</v>
       </c>
       <c r="F11">
-        <v>194.52239440807989</v>
+        <v>194.5223944080799</v>
       </c>
       <c r="G11">
-        <v>90.546215260631783</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>90.54621526063178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4615,22 +3079,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D12">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E12">
-        <v>101.63961030678929</v>
+        <v>101.6396103067893</v>
       </c>
       <c r="F12">
-        <v>203.86500705120551</v>
+        <v>203.8650070512055</v>
       </c>
       <c r="G12">
-        <v>94.836309447890187</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.83630944789019</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4638,22 +3102,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>23.161947170546629</v>
+        <v>23.16194717054663</v>
       </c>
       <c r="D13">
-        <v>47.282996053001177</v>
+        <v>47.28299605300118</v>
       </c>
       <c r="E13">
-        <v>95.558537873598212</v>
+        <v>95.55853787359821</v>
       </c>
       <c r="F13">
-        <v>192.07425435817319</v>
+        <v>192.0742543581732</v>
       </c>
       <c r="G13">
-        <v>89.519433863829803</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.5194338638298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4661,22 +3125,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D14">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E14">
         <v>102.5685424949238</v>
       </c>
       <c r="F14">
-        <v>208.30865786510151</v>
+        <v>208.3086578651015</v>
       </c>
       <c r="G14">
-        <v>96.179455198397804</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.1794551983978</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -4684,22 +3148,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D15">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E15">
         <v>103.1543289325507</v>
       </c>
       <c r="F15">
-        <v>210.65180361560911</v>
+        <v>210.6518036156091</v>
       </c>
       <c r="G15">
-        <v>96.911688245431435</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.91168824543144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4707,22 +3171,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>23.498473502456161</v>
+        <v>23.49847350245616</v>
       </c>
       <c r="D16">
-        <v>47.065518483523967</v>
+        <v>47.06551848352397</v>
       </c>
       <c r="E16">
-        <v>95.046057527679409</v>
+        <v>95.04605752767941</v>
       </c>
       <c r="F16">
-        <v>190.38679767235979</v>
+        <v>190.3867976723598</v>
       </c>
       <c r="G16">
-        <v>88.999211796504838</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>88.99921179650484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4730,10 +3194,10 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D17">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E17">
         <v>100.8111831820431</v>
@@ -4742,10 +3206,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G17">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4753,10 +3217,10 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D18">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E18">
         <v>100.8111831820431</v>
@@ -4765,10 +3229,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G18">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4776,22 +3240,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D19">
-        <v>49.698484809834987</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="E19">
         <v>100.8111831820431</v>
       </c>
       <c r="F19">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G19">
-        <v>98.143921292465052</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.14392129246505</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4799,10 +3263,10 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D20">
-        <v>49.698484809834987</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="E20">
         <v>100.8111831820431</v>
@@ -4811,10 +3275,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G20">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4822,10 +3286,10 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D21">
-        <v>49.698484809834987</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="E21">
         <v>100.8111831820431</v>
@@ -4834,10 +3298,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G21">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4845,22 +3309,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>23.672882102102211</v>
+        <v>23.67288210210221</v>
       </c>
       <c r="D22">
-        <v>48.253772353722432</v>
+        <v>48.25377235372243</v>
       </c>
       <c r="E22">
-        <v>98.032274851053927</v>
+        <v>98.03227485105393</v>
       </c>
       <c r="F22">
-        <v>193.78849164936241</v>
+        <v>193.7884916493624</v>
       </c>
       <c r="G22">
-        <v>90.936855239060236</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>90.93685523906024</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -4868,22 +3332,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>23.340092755419938</v>
+        <v>23.34009275541994</v>
       </c>
       <c r="D23">
-        <v>47.583889600220417</v>
+        <v>47.58388960022042</v>
       </c>
       <c r="E23">
-        <v>95.558537873598212</v>
+        <v>95.55853787359821</v>
       </c>
       <c r="F23">
-        <v>191.98143994131911</v>
+        <v>191.9814399413191</v>
       </c>
       <c r="G23">
-        <v>89.615990042639396</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.6159900426394</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4891,22 +3355,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D24">
-        <v>50.526911934581179</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="E24">
         <v>102.5685424949238</v>
       </c>
       <c r="F24">
-        <v>209.96551211459379</v>
+        <v>209.9655121145938</v>
       </c>
       <c r="G24">
-        <v>96.800775541957421</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.80077554195742</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4914,22 +3378,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D25">
-        <v>50.526911934581179</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="E25">
         <v>103.9827560572969</v>
       </c>
       <c r="F25">
-        <v>211.48023074035521</v>
+        <v>211.4802307403552</v>
       </c>
       <c r="G25">
-        <v>97.533008588991066</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.53300858899107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4937,13 +3401,13 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>23.562968604702139</v>
+        <v>23.56296860470214</v>
       </c>
       <c r="D26">
-        <v>47.065518483523967</v>
+        <v>47.06551848352397</v>
       </c>
       <c r="E26">
-        <v>95.046057527679409</v>
+        <v>95.04605752767941</v>
       </c>
       <c r="F26">
         <v>190.888811616704</v>
@@ -4952,7 +3416,7 @@
         <v>89.14083905815238</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4960,10 +3424,10 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D27">
-        <v>51.698484809834987</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="E27">
         <v>102.8111831820431</v>
@@ -4972,10 +3436,10 @@
         <v>205.3797256769669</v>
       </c>
       <c r="G27">
-        <v>96.007882323143974</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.00788232314397</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4983,22 +3447,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>23.607698869111029</v>
+        <v>23.60769886911103</v>
       </c>
       <c r="D28">
-        <v>48.393530838705423</v>
+        <v>48.39353083870542</v>
       </c>
       <c r="E28">
-        <v>97.729091725679922</v>
+        <v>97.72909172567992</v>
       </c>
       <c r="F28">
-        <v>192.43425302522229</v>
+        <v>192.4342530252223</v>
       </c>
       <c r="G28">
-        <v>90.541143614679669</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>90.54114361467967</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5006,22 +3470,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>23.316590932355599</v>
+        <v>23.3165909323556</v>
       </c>
       <c r="D29">
-        <v>47.282996053001177</v>
+        <v>47.28299605300118</v>
       </c>
       <c r="E29">
-        <v>95.479922773976583</v>
+        <v>95.47992277397658</v>
       </c>
       <c r="F29">
-        <v>192.10983334818101</v>
+        <v>192.109833348181</v>
       </c>
       <c r="G29">
-        <v>89.547335776878583</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.54733577687858</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5029,22 +3493,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>23.161947170546629</v>
+        <v>23.16194717054663</v>
       </c>
       <c r="D30">
-        <v>47.282996053001177</v>
+        <v>47.28299605300118</v>
       </c>
       <c r="E30">
-        <v>96.233789865496462</v>
+        <v>96.23378986549646</v>
       </c>
       <c r="F30">
         <v>193.4450255744953</v>
       </c>
       <c r="G30">
-        <v>90.030939665884887</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>90.03093966588489</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5052,22 +3516,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D31">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E31">
         <v>102.5685424949238</v>
       </c>
       <c r="F31">
-        <v>208.30865786510151</v>
+        <v>208.3086578651015</v>
       </c>
       <c r="G31">
-        <v>96.179455198397804</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.1794551983978</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5075,22 +3539,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>23.498473502456161</v>
+        <v>23.49847350245616</v>
       </c>
       <c r="D32">
-        <v>47.065518483523967</v>
+        <v>47.06551848352397</v>
       </c>
       <c r="E32">
-        <v>95.046057527679409</v>
+        <v>95.04605752767941</v>
       </c>
       <c r="F32">
-        <v>190.38679767235979</v>
+        <v>190.3867976723598</v>
       </c>
       <c r="G32">
-        <v>88.999211796504838</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>88.99921179650484</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5098,22 +3562,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D33">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E33">
         <v>100.8111831820431</v>
       </c>
       <c r="F33">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G33">
-        <v>98.143921292465052</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.14392129246505</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5121,10 +3585,10 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D34">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E34">
         <v>100.8111831820431</v>
@@ -5133,10 +3597,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G34">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5144,22 +3608,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>23.963990038857649</v>
+        <v>23.96399003885765</v>
       </c>
       <c r="D35">
-        <v>48.971601968780703</v>
+        <v>48.9716019687807</v>
       </c>
       <c r="E35">
-        <v>99.109206619708829</v>
+        <v>99.10920661970883</v>
       </c>
       <c r="F35">
-        <v>199.42457255008571</v>
+        <v>199.4245725500857</v>
       </c>
       <c r="G35">
-        <v>92.867342794358223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.86734279435822</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5167,22 +3631,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>23.785844453984339</v>
+        <v>23.78584445398434</v>
       </c>
       <c r="D36">
         <v>48.98590247034177</v>
       </c>
       <c r="E36">
-        <v>99.386018503056647</v>
+        <v>99.38601850305665</v>
       </c>
       <c r="F36">
-        <v>217.54088753375939</v>
+        <v>217.5408875337594</v>
       </c>
       <c r="G36">
-        <v>97.424663240285554</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.42466324028555</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5190,10 +3654,10 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D37">
-        <v>49.698484809834987</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="E37">
         <v>100.8111831820431</v>
@@ -5202,10 +3666,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G37">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5213,22 +3677,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>23.785844453984339</v>
+        <v>23.78584445398434</v>
       </c>
       <c r="D38">
         <v>48.98590247034177</v>
       </c>
       <c r="E38">
-        <v>99.386018503056647</v>
+        <v>99.38601850305665</v>
       </c>
       <c r="F38">
         <v>200.1862505684864</v>
       </c>
       <c r="G38">
-        <v>93.086003998967286</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.08600399896729</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -5236,22 +3700,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>23.316590932355599</v>
+        <v>23.3165909323556</v>
       </c>
       <c r="D39">
-        <v>47.713765670824401</v>
+        <v>47.7137656708244</v>
       </c>
       <c r="E39">
-        <v>95.479922773976583</v>
+        <v>95.47992277397658</v>
       </c>
       <c r="F39">
-        <v>191.90596330349749</v>
+        <v>191.9059633034975</v>
       </c>
       <c r="G39">
-        <v>89.604060670163506</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.60406067016351</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -5259,22 +3723,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>23.518238340293241</v>
+        <v>23.51823834029324</v>
       </c>
       <c r="D40">
-        <v>47.995578392494409</v>
+        <v>47.99557839249441</v>
       </c>
       <c r="E40">
-        <v>97.658954544482896</v>
+        <v>97.6589545444829</v>
       </c>
       <c r="F40">
         <v>193.4450255744953</v>
       </c>
       <c r="G40">
-        <v>90.654449212941458</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>90.65444921294146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -5282,22 +3746,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D41">
-        <v>50.526911934581179</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="E41">
         <v>103.39696961967</v>
       </c>
       <c r="F41">
-        <v>209.13708498984761</v>
+        <v>209.1370849898476</v>
       </c>
       <c r="G41">
-        <v>96.800775541957435</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.80077554195744</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -5305,10 +3769,10 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>23.320327917582851</v>
+        <v>23.32032791758285</v>
       </c>
       <c r="D42">
-        <v>47.194508688015937</v>
+        <v>47.19450868801594</v>
       </c>
       <c r="E42">
         <v>95.30403793666332</v>
@@ -5317,10 +3781,10 @@
         <v>190.888811616704</v>
       </c>
       <c r="G42">
-        <v>89.176921539741528</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.17692153974153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -5328,22 +3792,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>23.161947170546629</v>
+        <v>23.16194717054663</v>
       </c>
       <c r="D43">
-        <v>47.282996053001177</v>
+        <v>47.28299605300118</v>
       </c>
       <c r="E43">
-        <v>95.479922773976583</v>
+        <v>95.47992277397658</v>
       </c>
       <c r="F43">
-        <v>191.90596330349749</v>
+        <v>191.9059633034975</v>
       </c>
       <c r="G43">
         <v>89.45770732525547</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -5351,22 +3815,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>23.963990038857649</v>
+        <v>23.96399003885765</v>
       </c>
       <c r="D44">
-        <v>48.971601968780703</v>
+        <v>48.9716019687807</v>
       </c>
       <c r="E44">
-        <v>99.970296745915192</v>
+        <v>99.97029674591519</v>
       </c>
       <c r="F44">
-        <v>217.54088753375939</v>
+        <v>217.5408875337594</v>
       </c>
       <c r="G44">
-        <v>97.611694071828254</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.61169407182825</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -5374,10 +3838,10 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D45">
-        <v>49.698484809835001</v>
+        <v>49.698484809835</v>
       </c>
       <c r="E45">
         <v>100.8111831820431</v>
@@ -5386,10 +3850,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G45">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -5397,22 +3861,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>23.963990038857649</v>
+        <v>23.96399003885765</v>
       </c>
       <c r="D46">
-        <v>48.971601968780703</v>
+        <v>48.9716019687807</v>
       </c>
       <c r="E46">
-        <v>99.109206619708829</v>
+        <v>99.10920661970883</v>
       </c>
       <c r="F46">
-        <v>199.42457255008571</v>
+        <v>199.4245725500857</v>
       </c>
       <c r="G46">
-        <v>92.867342794358223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.86734279435822</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -5420,22 +3884,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>23.785844453984339</v>
+        <v>23.78584445398434</v>
       </c>
       <c r="D47">
         <v>48.98590247034177</v>
       </c>
       <c r="E47">
-        <v>99.386018503056647</v>
+        <v>99.38601850305665</v>
       </c>
       <c r="F47">
         <v>200.1862505684864</v>
       </c>
       <c r="G47">
-        <v>93.086003998967286</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.08600399896729</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -5443,22 +3907,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>23.340092755419938</v>
+        <v>23.34009275541994</v>
       </c>
       <c r="D48">
-        <v>47.995578392494409</v>
+        <v>47.99557839249441</v>
       </c>
       <c r="E48">
-        <v>95.692041512682138</v>
+        <v>95.69204151268214</v>
       </c>
       <c r="F48">
-        <v>191.90596330349749</v>
+        <v>191.9059633034975</v>
       </c>
       <c r="G48">
-        <v>89.733418991023484</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.73341899102348</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -5466,19 +3930,19 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>23.963990038857649</v>
+        <v>23.96399003885765</v>
       </c>
       <c r="D49">
-        <v>48.971601968780703</v>
+        <v>48.9716019687807</v>
       </c>
       <c r="E49">
-        <v>99.109206619708829</v>
+        <v>99.10920661970883</v>
       </c>
       <c r="F49">
-        <v>199.42457255008571</v>
+        <v>199.4245725500857</v>
       </c>
       <c r="G49">
-        <v>92.867342794358223</v>
+        <v>92.86734279435822</v>
       </c>
     </row>
   </sheetData>
@@ -5487,11 +3951,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5514,7 +3978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5537,7 +4001,7 @@
         <v>162.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5560,7 +4024,7 @@
         <v>364.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5583,7 +4047,7 @@
         <v>241.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5606,7 +4070,7 @@
         <v>308.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5629,7 +4093,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5652,7 +4116,7 @@
         <v>162.75</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5675,7 +4139,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5698,7 +4162,7 @@
         <v>289.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5721,7 +4185,7 @@
         <v>304.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5744,7 +4208,7 @@
         <v>364.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5767,7 +4231,7 @@
         <v>298.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5790,7 +4254,7 @@
         <v>241.25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5813,7 +4277,7 @@
         <v>245.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5836,7 +4300,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5859,7 +4323,7 @@
         <v>308.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5882,7 +4346,7 @@
         <v>331.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5905,7 +4369,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5928,7 +4392,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5951,7 +4415,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5974,7 +4438,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5997,7 +4461,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -6020,7 +4484,7 @@
         <v>289.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -6043,7 +4507,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -6066,7 +4530,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -6089,7 +4553,7 @@
         <v>304.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -6112,7 +4576,7 @@
         <v>329.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -6135,7 +4599,7 @@
         <v>298.25</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -6158,7 +4622,7 @@
         <v>245.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -6181,7 +4645,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -6204,7 +4668,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -6227,7 +4691,7 @@
         <v>331.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -6250,7 +4714,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -6273,7 +4737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6296,7 +4760,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6319,7 +4783,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -6342,7 +4806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -6365,7 +4829,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -6388,7 +4852,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -6411,7 +4875,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -6434,7 +4898,7 @@
         <v>294.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -6457,7 +4921,7 @@
         <v>329.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -6480,7 +4944,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6503,7 +4967,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6526,7 +4990,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6549,7 +5013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6572,7 +5036,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -6595,7 +5059,7 @@
         <v>294.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -6624,11 +5088,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6651,7 +5115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6674,7 +5138,7 @@
         <v>1315.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6697,7 +5161,7 @@
         <v>1097.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6720,7 +5184,7 @@
         <v>179.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6743,7 +5207,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6766,7 +5230,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6789,7 +5253,7 @@
         <v>1315.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6812,7 +5276,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6835,7 +5299,7 @@
         <v>206.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6858,7 +5322,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6881,7 +5345,7 @@
         <v>1097.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6904,7 +5368,7 @@
         <v>1071.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6927,7 +5391,7 @@
         <v>179.25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6950,7 +5414,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6973,7 +5437,7 @@
         <v>247.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6996,7 +5460,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7019,7 +5483,7 @@
         <v>685.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7042,7 +5506,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7065,7 +5529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7088,7 +5552,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7111,7 +5575,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7134,7 +5598,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -7157,7 +5621,7 @@
         <v>206.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7180,7 +5644,7 @@
         <v>210.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7203,7 +5667,7 @@
         <v>342.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7226,7 +5690,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7249,7 +5713,7 @@
         <v>868.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7272,7 +5736,7 @@
         <v>1071.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7295,7 +5759,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7318,7 +5782,7 @@
         <v>247.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7341,7 +5805,7 @@
         <v>213.75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7364,7 +5828,7 @@
         <v>685.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7387,7 +5851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7410,7 +5874,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7433,7 +5897,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7456,7 +5920,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7479,7 +5943,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7502,7 +5966,7 @@
         <v>31.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -7525,7 +5989,7 @@
         <v>210.75</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -7548,7 +6012,7 @@
         <v>342.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -7571,7 +6035,7 @@
         <v>293.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -7594,7 +6058,7 @@
         <v>868.25</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -7617,7 +6081,7 @@
         <v>213.75</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7640,7 +6104,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7663,7 +6127,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7686,7 +6150,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7709,7 +6173,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -7732,7 +6196,7 @@
         <v>293.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -7761,11 +6225,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7788,7 +6252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7811,7 +6275,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7834,7 +6298,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7857,7 +6321,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -7880,7 +6344,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -7903,7 +6367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -7926,7 +6390,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -7949,7 +6413,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -7972,7 +6436,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7995,7 +6459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8018,7 +6482,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8041,7 +6505,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8064,7 +6528,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8087,7 +6551,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8110,7 +6574,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8133,7 +6597,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8156,7 +6620,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8179,7 +6643,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8202,7 +6666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8225,7 +6689,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8248,7 +6712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8271,7 +6735,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8294,7 +6758,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8317,7 +6781,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8340,7 +6804,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8363,7 +6827,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8386,7 +6850,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8409,7 +6873,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8432,7 +6896,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8455,7 +6919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8478,7 +6942,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8501,7 +6965,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8524,7 +6988,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8547,7 +7011,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8570,7 +7034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8593,7 +7057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8616,7 +7080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8639,7 +7103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -8662,7 +7126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -8685,7 +7149,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -8708,7 +7172,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -8731,7 +7195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -8754,7 +7218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -8777,7 +7241,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -8800,7 +7264,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -8823,7 +7287,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -8846,7 +7310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -8869,7 +7333,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_128_avg_length.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9644C63-DD1A-4F28-A9FC-C0B7C4FEB2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33C5F02-4AC1-473A-86D0-98E0F027D9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
     <sheet name="Jumlah Simpul" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Jumlah Belok'!$A$1:$G$49</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -217,6 +220,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -294,10 +298,4554 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Waktu Pencarian (Map A)</a:t>
+            </a:r>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="36000" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.3960000000000011E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3719000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.38073E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15643599999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B8F2-41D9-8B3E-743FCE9BF74D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.0099999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2424000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3069000000000007E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.7966600000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B8F2-41D9-8B3E-743FCE9BF74D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.6440000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.8204E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.22614E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.2469199999999993E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B8F2-41D9-8B3E-743FCE9BF74D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltDnDiag">
+              <a:fgClr>
+                <a:srgbClr val="92D050"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="00B050"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.7369999999999998E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0735E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.4778999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4384299999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B8F2-41D9-8B3E-743FCE9BF74D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-10"/>
+        <c:axId val="1624727792"/>
+        <c:axId val="1624720112"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1624727792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Ukuran Map</a:t>
+                </a:r>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1624720112"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1624720112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.16000000000000003"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1624727792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.75927384076991E-2"/>
+          <c:y val="0.1727734825847049"/>
+          <c:w val="8.462948381452319E-2"/>
+          <c:h val="0.30803792801610952"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Jumlah Belokan</a:t>
+            </a:r>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Belok'!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1146-42AE-A072-45324852D574}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PPO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltDnDiag">
+              <a:fgClr>
+                <a:srgbClr val="00B050"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="92D050"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Belok'!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1146-42AE-A072-45324852D574}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Belok'!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1146-42AE-A072-45324852D574}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Belok'!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1146-42AE-A072-45324852D574}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Belok'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Belok'!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-1146-42AE-A072-45324852D574}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-10"/>
+        <c:axId val="176046543"/>
+        <c:axId val="176044143"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="176046543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Ukuran Map</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="176044143"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="176044143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="176046543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="l"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.6666666666666666E-2"/>
+          <c:y val="0.17063502478856807"/>
+          <c:w val="8.651815398075241E-2"/>
+          <c:h val="0.30927698886306398"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Jumlah Simpul</a:t>
+            </a:r>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Simpul'!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1149</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4358</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-28A7-4F6A-960E-F5149AFEEA2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Simpul'!$B$4:$E$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>348</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>987</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-28A7-4F6A-960E-F5149AFEEA2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Simpul'!$B$5:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>259</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>841</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2765</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-28A7-4F6A-960E-F5149AFEEA2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="pct50">
+              <a:fgClr>
+                <a:srgbClr val="92D050"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="00B050"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Jumlah Simpul'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Jumlah Simpul'!$B$6:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-28A7-4F6A-960E-F5149AFEEA2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="-10"/>
+        <c:axId val="1749884256"/>
+        <c:axId val="1749887136"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1749884256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Ukuran Map</a:t>
+                </a:r>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1749887136"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1749887136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1749884256"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="l"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.166666666666666E-2"/>
+          <c:y val="0.16340150189559638"/>
+          <c:w val="8.462948381452319E-2"/>
+          <c:h val="0.30803792801610952"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>128214</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27996</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>433014</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>27995</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10E6543E-C6AB-31AD-7B47-02B4A7BB1369}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{496998F5-90D3-F3B0-9427-D64B56E982DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>429370</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>93925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>124570</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>93924</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E21DF28-E833-6DCC-8A77-781277CF741B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1714,6 +6262,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6269,6 +10818,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -6321,22 +10873,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>10.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -6344,22 +10896,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -6367,22 +10919,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
+      <c r="E5">
         <v>14</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>12</v>
       </c>
-      <c r="F5">
-        <v>14</v>
-      </c>
       <c r="G5">
-        <v>12.75</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6390,22 +10942,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
         <v>11</v>
       </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
       <c r="D6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -6413,22 +10965,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
         <v>12</v>
       </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
       <c r="F7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -6436,22 +10988,22 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>10</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>12.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -6459,22 +11011,22 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>12.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -6482,22 +11034,22 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>16</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -6505,10 +11057,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -6520,7 +11072,7 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -6528,22 +11080,22 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>11.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -6551,22 +11103,22 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -6574,22 +11126,22 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -6597,22 +11149,22 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>11.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -6620,22 +11172,22 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -6643,22 +11195,22 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>11</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="F17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>12.75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -6666,22 +11218,22 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C18">
         <v>7</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G18">
-        <v>7.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -6689,22 +11241,22 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G19">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -6712,22 +11264,22 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -6735,22 +11287,22 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -6758,22 +11310,22 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G22">
-        <v>5.25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -6804,22 +11356,22 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>12</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -6827,22 +11379,22 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F25">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>14.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -6850,22 +11402,22 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
         <v>6</v>
       </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26">
-        <v>6</v>
-      </c>
-      <c r="F26">
-        <v>7</v>
-      </c>
       <c r="G26">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -6873,22 +11425,22 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>17.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -6896,22 +11448,22 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -6919,22 +11471,22 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -6942,22 +11494,22 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -6965,22 +11517,22 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G31">
-        <v>12</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -6988,22 +11540,22 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -7057,22 +11609,22 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -7080,22 +11632,22 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -7103,22 +11655,22 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E37">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -7126,22 +11678,22 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -7195,22 +11747,22 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>14.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -7218,22 +11770,22 @@
         <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>6.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -7241,22 +11793,22 @@
         <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -7264,22 +11816,22 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C44">
         <v>6</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -7287,22 +11839,22 @@
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C45">
+        <v>6</v>
+      </c>
+      <c r="D45">
         <v>7</v>
       </c>
-      <c r="D45">
-        <v>8</v>
-      </c>
       <c r="E45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G45">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -7310,22 +11862,22 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -7333,22 +11885,22 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -7398,7 +11950,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G49" xr:uid="{00000000-0001-0000-0500-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G49">
+      <sortCondition ref="A1:A49"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8242,5 +12800,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>